--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_7_13.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_7_13.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>177858.1756706893</v>
+        <v>176377.9162303366</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5455336.352214552</v>
+        <v>5464686.089830845</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22712646.72816689</v>
+        <v>22709644.84263526</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3981389.625307065</v>
+        <v>3982153.632669994</v>
       </c>
     </row>
     <row r="11">
@@ -8670,22 +8670,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>218.5557354670911</v>
+        <v>218.2111409464629</v>
       </c>
       <c r="L11" t="n">
-        <v>233.8632089398365</v>
+        <v>233.4357089658653</v>
       </c>
       <c r="M11" t="n">
-        <v>228.2285498101873</v>
+        <v>227.7528737187178</v>
       </c>
       <c r="N11" t="n">
-        <v>227.2611138478472</v>
+        <v>226.7777408199137</v>
       </c>
       <c r="O11" t="n">
-        <v>228.0661862960586</v>
+        <v>227.6097508526263</v>
       </c>
       <c r="P11" t="n">
-        <v>229.4987093231087</v>
+        <v>229.1091522321465</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8749,25 +8749,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>136.7994484083212</v>
+        <v>136.5653954824675</v>
       </c>
       <c r="L12" t="n">
-        <v>137.1532948742138</v>
+        <v>136.8385818314783</v>
       </c>
       <c r="M12" t="n">
-        <v>140.4990339220183</v>
+        <v>140.1317786452013</v>
       </c>
       <c r="N12" t="n">
-        <v>129.6634384984276</v>
+        <v>129.2864630672354</v>
       </c>
       <c r="O12" t="n">
-        <v>141.0609519916142</v>
+        <v>140.7160931202018</v>
       </c>
       <c r="P12" t="n">
-        <v>132.7421998671604</v>
+        <v>132.4654202195568</v>
       </c>
       <c r="Q12" t="n">
-        <v>139.158075972814</v>
+        <v>138.9730561082392</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,16 +8831,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>134.0803811992711</v>
+        <v>133.8997196622861</v>
       </c>
       <c r="M13" t="n">
-        <v>138.0777675541624</v>
+        <v>137.8872852940284</v>
       </c>
       <c r="N13" t="n">
-        <v>126.8576920062168</v>
+        <v>126.6717389884799</v>
       </c>
       <c r="O13" t="n">
-        <v>137.6918827141379</v>
+        <v>137.5201250048898</v>
       </c>
       <c r="P13" t="n">
         <v>135.0065633140411</v>
@@ -8907,22 +8907,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>218.5557354670911</v>
+        <v>218.2111409464629</v>
       </c>
       <c r="L14" t="n">
-        <v>233.8632089398365</v>
+        <v>233.4357089658653</v>
       </c>
       <c r="M14" t="n">
-        <v>228.2285498101873</v>
+        <v>227.7528737187178</v>
       </c>
       <c r="N14" t="n">
-        <v>227.2611138478472</v>
+        <v>226.7777408199137</v>
       </c>
       <c r="O14" t="n">
-        <v>228.0661862960586</v>
+        <v>227.6097508526263</v>
       </c>
       <c r="P14" t="n">
-        <v>229.4987093231087</v>
+        <v>229.1091522321465</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,25 +8986,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>136.7994484083212</v>
+        <v>136.5653954824675</v>
       </c>
       <c r="L15" t="n">
-        <v>137.1532948742138</v>
+        <v>136.8385818314783</v>
       </c>
       <c r="M15" t="n">
-        <v>140.4990339220183</v>
+        <v>140.1317786452013</v>
       </c>
       <c r="N15" t="n">
-        <v>129.6634384984276</v>
+        <v>129.2864630672354</v>
       </c>
       <c r="O15" t="n">
-        <v>141.0609519916142</v>
+        <v>140.7160931202018</v>
       </c>
       <c r="P15" t="n">
-        <v>132.7421998671604</v>
+        <v>132.4654202195568</v>
       </c>
       <c r="Q15" t="n">
-        <v>139.158075972814</v>
+        <v>138.9730561082392</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,16 +9068,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>134.0803811992711</v>
+        <v>133.8997196622861</v>
       </c>
       <c r="M16" t="n">
-        <v>138.0777675541624</v>
+        <v>137.8872852940284</v>
       </c>
       <c r="N16" t="n">
-        <v>126.8576920062168</v>
+        <v>126.6717389884799</v>
       </c>
       <c r="O16" t="n">
-        <v>137.6918827141379</v>
+        <v>137.5201250048898</v>
       </c>
       <c r="P16" t="n">
         <v>135.0065633140411</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>218.5557354670911</v>
+        <v>218.2111409464629</v>
       </c>
       <c r="L17" t="n">
-        <v>233.8632089398365</v>
+        <v>233.4357089658653</v>
       </c>
       <c r="M17" t="n">
-        <v>228.2285498101873</v>
+        <v>227.7528737187178</v>
       </c>
       <c r="N17" t="n">
-        <v>227.2611138478472</v>
+        <v>226.7777408199137</v>
       </c>
       <c r="O17" t="n">
-        <v>228.0661862960586</v>
+        <v>227.6097508526263</v>
       </c>
       <c r="P17" t="n">
-        <v>229.4987093231087</v>
+        <v>229.1091522321465</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9223,25 +9223,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>136.7994484083212</v>
+        <v>136.5653954824675</v>
       </c>
       <c r="L18" t="n">
-        <v>137.1532948742138</v>
+        <v>136.8385818314783</v>
       </c>
       <c r="M18" t="n">
-        <v>140.4990339220183</v>
+        <v>140.1317786452013</v>
       </c>
       <c r="N18" t="n">
-        <v>129.6634384984276</v>
+        <v>129.2864630672354</v>
       </c>
       <c r="O18" t="n">
-        <v>141.0609519916142</v>
+        <v>140.7160931202018</v>
       </c>
       <c r="P18" t="n">
-        <v>132.7421998671604</v>
+        <v>132.4654202195568</v>
       </c>
       <c r="Q18" t="n">
-        <v>139.158075972814</v>
+        <v>138.9730561082392</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9305,16 +9305,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L19" t="n">
-        <v>134.0803811992711</v>
+        <v>133.8997196622861</v>
       </c>
       <c r="M19" t="n">
-        <v>138.0777675541624</v>
+        <v>137.8872852940284</v>
       </c>
       <c r="N19" t="n">
-        <v>126.8576920062168</v>
+        <v>126.6717389884799</v>
       </c>
       <c r="O19" t="n">
-        <v>137.6918827141379</v>
+        <v>137.5201250048898</v>
       </c>
       <c r="P19" t="n">
         <v>135.0065633140411</v>
@@ -9381,22 +9381,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>218.5557354670911</v>
+        <v>218.2111409464629</v>
       </c>
       <c r="L20" t="n">
-        <v>233.8632089398365</v>
+        <v>233.4357089658653</v>
       </c>
       <c r="M20" t="n">
-        <v>228.2285498101873</v>
+        <v>227.7528737187178</v>
       </c>
       <c r="N20" t="n">
-        <v>227.2611138478472</v>
+        <v>226.7777408199137</v>
       </c>
       <c r="O20" t="n">
-        <v>228.0661862960586</v>
+        <v>227.6097508526263</v>
       </c>
       <c r="P20" t="n">
-        <v>229.4987093231087</v>
+        <v>229.1091522321465</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9460,25 +9460,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>136.7994484083212</v>
+        <v>136.5653954824675</v>
       </c>
       <c r="L21" t="n">
-        <v>137.1532948742138</v>
+        <v>136.8385818314783</v>
       </c>
       <c r="M21" t="n">
-        <v>140.4990339220183</v>
+        <v>140.1317786452013</v>
       </c>
       <c r="N21" t="n">
-        <v>129.6634384984276</v>
+        <v>129.2864630672354</v>
       </c>
       <c r="O21" t="n">
-        <v>141.0609519916142</v>
+        <v>140.7160931202018</v>
       </c>
       <c r="P21" t="n">
-        <v>132.7421998671604</v>
+        <v>132.4654202195568</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.158075972814</v>
+        <v>138.9730561082392</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9542,16 +9542,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L22" t="n">
-        <v>134.0803811992711</v>
+        <v>133.8997196622861</v>
       </c>
       <c r="M22" t="n">
-        <v>138.0777675541624</v>
+        <v>137.8872852940284</v>
       </c>
       <c r="N22" t="n">
-        <v>126.8576920062168</v>
+        <v>126.6717389884799</v>
       </c>
       <c r="O22" t="n">
-        <v>137.6918827141379</v>
+        <v>137.5201250048898</v>
       </c>
       <c r="P22" t="n">
         <v>135.0065633140411</v>
@@ -9618,22 +9618,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>218.5557354670911</v>
+        <v>218.2111409464629</v>
       </c>
       <c r="L23" t="n">
-        <v>233.8632089398365</v>
+        <v>233.4357089658653</v>
       </c>
       <c r="M23" t="n">
-        <v>228.2285498101873</v>
+        <v>227.7528737187178</v>
       </c>
       <c r="N23" t="n">
-        <v>227.2611138478472</v>
+        <v>226.7777408199137</v>
       </c>
       <c r="O23" t="n">
-        <v>228.0661862960586</v>
+        <v>227.6097508526263</v>
       </c>
       <c r="P23" t="n">
-        <v>229.4987093231087</v>
+        <v>229.1091522321465</v>
       </c>
       <c r="Q23" t="n">
         <v>212.3149906599047</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>136.7994484083212</v>
+        <v>136.5653954824675</v>
       </c>
       <c r="L24" t="n">
-        <v>137.1532948742138</v>
+        <v>136.8385818314783</v>
       </c>
       <c r="M24" t="n">
-        <v>140.4990339220183</v>
+        <v>140.1317786452013</v>
       </c>
       <c r="N24" t="n">
-        <v>129.6634384984276</v>
+        <v>129.2864630672354</v>
       </c>
       <c r="O24" t="n">
-        <v>141.0609519916142</v>
+        <v>140.7160931202018</v>
       </c>
       <c r="P24" t="n">
-        <v>132.7421998671604</v>
+        <v>132.4654202195568</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.158075972814</v>
+        <v>138.9730561082392</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9779,16 +9779,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L25" t="n">
-        <v>134.0803811992711</v>
+        <v>133.8997196622861</v>
       </c>
       <c r="M25" t="n">
-        <v>138.0777675541624</v>
+        <v>137.8872852940284</v>
       </c>
       <c r="N25" t="n">
-        <v>126.8576920062168</v>
+        <v>126.6717389884799</v>
       </c>
       <c r="O25" t="n">
-        <v>137.6918827141379</v>
+        <v>137.5201250048898</v>
       </c>
       <c r="P25" t="n">
         <v>135.0065633140411</v>
@@ -9855,22 +9855,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>218.5557354670911</v>
+        <v>218.2111409464629</v>
       </c>
       <c r="L26" t="n">
-        <v>233.8632089398365</v>
+        <v>233.4357089658653</v>
       </c>
       <c r="M26" t="n">
-        <v>228.2285498101873</v>
+        <v>227.7528737187178</v>
       </c>
       <c r="N26" t="n">
-        <v>227.2611138478472</v>
+        <v>226.7777408199137</v>
       </c>
       <c r="O26" t="n">
-        <v>228.0661862960586</v>
+        <v>227.6097508526263</v>
       </c>
       <c r="P26" t="n">
-        <v>229.4987093231087</v>
+        <v>229.1091522321465</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9934,25 +9934,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>136.7994484083212</v>
+        <v>136.5653954824675</v>
       </c>
       <c r="L27" t="n">
-        <v>137.1532948742138</v>
+        <v>136.8385818314783</v>
       </c>
       <c r="M27" t="n">
-        <v>140.4990339220183</v>
+        <v>140.1317786452013</v>
       </c>
       <c r="N27" t="n">
-        <v>129.6634384984276</v>
+        <v>129.2864630672354</v>
       </c>
       <c r="O27" t="n">
-        <v>141.0609519916142</v>
+        <v>140.7160931202018</v>
       </c>
       <c r="P27" t="n">
-        <v>132.7421998671604</v>
+        <v>132.4654202195568</v>
       </c>
       <c r="Q27" t="n">
-        <v>139.158075972814</v>
+        <v>138.9730561082392</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10016,16 +10016,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L28" t="n">
-        <v>134.0803811992711</v>
+        <v>133.8997196622861</v>
       </c>
       <c r="M28" t="n">
-        <v>138.0777675541624</v>
+        <v>137.8872852940284</v>
       </c>
       <c r="N28" t="n">
-        <v>126.8576920062168</v>
+        <v>126.6717389884799</v>
       </c>
       <c r="O28" t="n">
-        <v>137.6918827141379</v>
+        <v>137.5201250048898</v>
       </c>
       <c r="P28" t="n">
         <v>135.0065633140411</v>
@@ -10092,22 +10092,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>218.5557354670911</v>
+        <v>218.2111409464629</v>
       </c>
       <c r="L29" t="n">
-        <v>233.8632089398365</v>
+        <v>233.4357089658653</v>
       </c>
       <c r="M29" t="n">
-        <v>228.2285498101873</v>
+        <v>227.7528737187178</v>
       </c>
       <c r="N29" t="n">
-        <v>227.2611138478472</v>
+        <v>226.7777408199137</v>
       </c>
       <c r="O29" t="n">
-        <v>228.0661862960586</v>
+        <v>227.6097508526263</v>
       </c>
       <c r="P29" t="n">
-        <v>229.4987093231087</v>
+        <v>229.1091522321465</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10171,25 +10171,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>136.7994484083212</v>
+        <v>136.5653954824675</v>
       </c>
       <c r="L30" t="n">
-        <v>137.1532948742138</v>
+        <v>136.8385818314783</v>
       </c>
       <c r="M30" t="n">
-        <v>140.4990339220183</v>
+        <v>140.1317786452013</v>
       </c>
       <c r="N30" t="n">
-        <v>129.6634384984276</v>
+        <v>129.2864630672354</v>
       </c>
       <c r="O30" t="n">
-        <v>141.0609519916142</v>
+        <v>140.7160931202018</v>
       </c>
       <c r="P30" t="n">
-        <v>132.7421998671604</v>
+        <v>132.4654202195568</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.158075972814</v>
+        <v>138.9730561082392</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10253,16 +10253,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L31" t="n">
-        <v>134.0803811992711</v>
+        <v>133.8997196622861</v>
       </c>
       <c r="M31" t="n">
-        <v>138.0777675541624</v>
+        <v>137.8872852940284</v>
       </c>
       <c r="N31" t="n">
-        <v>126.8576920062168</v>
+        <v>126.6717389884799</v>
       </c>
       <c r="O31" t="n">
-        <v>137.6918827141379</v>
+        <v>137.5201250048898</v>
       </c>
       <c r="P31" t="n">
         <v>135.0065633140411</v>
@@ -10329,22 +10329,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>218.5557354670911</v>
+        <v>218.2111409464629</v>
       </c>
       <c r="L32" t="n">
-        <v>233.8632089398365</v>
+        <v>233.4357089658653</v>
       </c>
       <c r="M32" t="n">
-        <v>228.2285498101873</v>
+        <v>227.7528737187178</v>
       </c>
       <c r="N32" t="n">
-        <v>227.2611138478472</v>
+        <v>226.7777408199137</v>
       </c>
       <c r="O32" t="n">
-        <v>228.0661862960586</v>
+        <v>227.6097508526263</v>
       </c>
       <c r="P32" t="n">
-        <v>229.4987093231087</v>
+        <v>229.1091522321465</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10408,25 +10408,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>136.7994484083212</v>
+        <v>136.5653954824675</v>
       </c>
       <c r="L33" t="n">
-        <v>137.1532948742138</v>
+        <v>136.8385818314783</v>
       </c>
       <c r="M33" t="n">
-        <v>140.4990339220183</v>
+        <v>140.1317786452013</v>
       </c>
       <c r="N33" t="n">
-        <v>129.6634384984276</v>
+        <v>129.2864630672354</v>
       </c>
       <c r="O33" t="n">
-        <v>141.0609519916142</v>
+        <v>140.7160931202018</v>
       </c>
       <c r="P33" t="n">
-        <v>132.7421998671604</v>
+        <v>132.4654202195568</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.158075972814</v>
+        <v>138.9730561082392</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10490,16 +10490,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L34" t="n">
-        <v>134.0803811992711</v>
+        <v>133.8997196622861</v>
       </c>
       <c r="M34" t="n">
-        <v>138.0777675541624</v>
+        <v>137.8872852940284</v>
       </c>
       <c r="N34" t="n">
-        <v>126.8576920062168</v>
+        <v>126.6717389884799</v>
       </c>
       <c r="O34" t="n">
-        <v>137.6918827141379</v>
+        <v>137.5201250048898</v>
       </c>
       <c r="P34" t="n">
         <v>135.0065633140411</v>
@@ -10566,22 +10566,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>218.5557354670911</v>
+        <v>218.2111409464629</v>
       </c>
       <c r="L35" t="n">
-        <v>233.8632089398365</v>
+        <v>233.4357089658653</v>
       </c>
       <c r="M35" t="n">
-        <v>228.2285498101873</v>
+        <v>227.7528737187178</v>
       </c>
       <c r="N35" t="n">
-        <v>227.2611138478472</v>
+        <v>226.7777408199137</v>
       </c>
       <c r="O35" t="n">
-        <v>228.0661862960586</v>
+        <v>227.6097508526263</v>
       </c>
       <c r="P35" t="n">
-        <v>229.4987093231087</v>
+        <v>229.1091522321465</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10645,25 +10645,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>136.7994484083212</v>
+        <v>136.5653954824675</v>
       </c>
       <c r="L36" t="n">
-        <v>137.1532948742138</v>
+        <v>136.8385818314783</v>
       </c>
       <c r="M36" t="n">
-        <v>140.4990339220183</v>
+        <v>140.1317786452013</v>
       </c>
       <c r="N36" t="n">
-        <v>129.6634384984276</v>
+        <v>129.2864630672354</v>
       </c>
       <c r="O36" t="n">
-        <v>141.0609519916142</v>
+        <v>140.7160931202018</v>
       </c>
       <c r="P36" t="n">
-        <v>132.7421998671604</v>
+        <v>132.4654202195568</v>
       </c>
       <c r="Q36" t="n">
-        <v>139.158075972814</v>
+        <v>138.9730561082392</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10727,16 +10727,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L37" t="n">
-        <v>134.0803811992711</v>
+        <v>133.8997196622861</v>
       </c>
       <c r="M37" t="n">
-        <v>138.0777675541624</v>
+        <v>137.8872852940284</v>
       </c>
       <c r="N37" t="n">
-        <v>126.8576920062168</v>
+        <v>126.6717389884799</v>
       </c>
       <c r="O37" t="n">
-        <v>137.6918827141379</v>
+        <v>137.5201250048898</v>
       </c>
       <c r="P37" t="n">
         <v>135.0065633140411</v>
@@ -10803,22 +10803,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>218.5557354670911</v>
+        <v>218.2111409464629</v>
       </c>
       <c r="L38" t="n">
-        <v>233.8632089398365</v>
+        <v>233.4357089658653</v>
       </c>
       <c r="M38" t="n">
-        <v>228.2285498101873</v>
+        <v>227.7528737187178</v>
       </c>
       <c r="N38" t="n">
-        <v>227.2611138478472</v>
+        <v>226.7777408199137</v>
       </c>
       <c r="O38" t="n">
-        <v>228.0661862960586</v>
+        <v>227.6097508526263</v>
       </c>
       <c r="P38" t="n">
-        <v>229.4987093231087</v>
+        <v>229.1091522321465</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10882,25 +10882,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>136.7994484083212</v>
+        <v>136.5653954824675</v>
       </c>
       <c r="L39" t="n">
-        <v>137.1532948742138</v>
+        <v>136.8385818314783</v>
       </c>
       <c r="M39" t="n">
-        <v>140.4990339220183</v>
+        <v>140.1317786452013</v>
       </c>
       <c r="N39" t="n">
-        <v>129.6634384984276</v>
+        <v>129.2864630672354</v>
       </c>
       <c r="O39" t="n">
-        <v>141.0609519916142</v>
+        <v>140.7160931202018</v>
       </c>
       <c r="P39" t="n">
-        <v>132.7421998671604</v>
+        <v>132.4654202195568</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.158075972814</v>
+        <v>138.9730561082392</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10964,16 +10964,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L40" t="n">
-        <v>134.0803811992711</v>
+        <v>133.8997196622861</v>
       </c>
       <c r="M40" t="n">
-        <v>138.0777675541624</v>
+        <v>137.8872852940284</v>
       </c>
       <c r="N40" t="n">
-        <v>126.8576920062168</v>
+        <v>126.6717389884799</v>
       </c>
       <c r="O40" t="n">
-        <v>137.6918827141379</v>
+        <v>137.5201250048898</v>
       </c>
       <c r="P40" t="n">
         <v>135.0065633140411</v>
@@ -11040,22 +11040,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>218.5557354670911</v>
+        <v>218.2111409464629</v>
       </c>
       <c r="L41" t="n">
-        <v>233.8632089398365</v>
+        <v>233.4357089658653</v>
       </c>
       <c r="M41" t="n">
-        <v>228.2285498101873</v>
+        <v>227.7528737187178</v>
       </c>
       <c r="N41" t="n">
-        <v>227.2611138478472</v>
+        <v>226.7777408199137</v>
       </c>
       <c r="O41" t="n">
-        <v>228.0661862960586</v>
+        <v>227.6097508526263</v>
       </c>
       <c r="P41" t="n">
-        <v>229.4987093231087</v>
+        <v>229.1091522321465</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11119,25 +11119,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>136.7994484083212</v>
+        <v>136.5653954824675</v>
       </c>
       <c r="L42" t="n">
-        <v>137.1532948742138</v>
+        <v>136.8385818314783</v>
       </c>
       <c r="M42" t="n">
-        <v>140.4990339220183</v>
+        <v>140.1317786452013</v>
       </c>
       <c r="N42" t="n">
-        <v>129.6634384984276</v>
+        <v>129.2864630672354</v>
       </c>
       <c r="O42" t="n">
-        <v>141.0609519916142</v>
+        <v>140.7160931202018</v>
       </c>
       <c r="P42" t="n">
-        <v>132.7421998671604</v>
+        <v>132.4654202195568</v>
       </c>
       <c r="Q42" t="n">
-        <v>139.158075972814</v>
+        <v>138.9730561082392</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11201,16 +11201,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L43" t="n">
-        <v>134.0803811992711</v>
+        <v>133.8997196622861</v>
       </c>
       <c r="M43" t="n">
-        <v>138.0777675541624</v>
+        <v>137.8872852940284</v>
       </c>
       <c r="N43" t="n">
-        <v>126.8576920062168</v>
+        <v>126.6717389884799</v>
       </c>
       <c r="O43" t="n">
-        <v>137.6918827141379</v>
+        <v>137.5201250048898</v>
       </c>
       <c r="P43" t="n">
         <v>135.0065633140411</v>
@@ -11277,22 +11277,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K44" t="n">
-        <v>218.5557354670911</v>
+        <v>218.2111409464629</v>
       </c>
       <c r="L44" t="n">
-        <v>233.8632089398365</v>
+        <v>233.4357089658653</v>
       </c>
       <c r="M44" t="n">
-        <v>228.2285498101873</v>
+        <v>227.7528737187178</v>
       </c>
       <c r="N44" t="n">
-        <v>227.2611138478472</v>
+        <v>226.7777408199137</v>
       </c>
       <c r="O44" t="n">
-        <v>228.0661862960586</v>
+        <v>227.6097508526263</v>
       </c>
       <c r="P44" t="n">
-        <v>229.4987093231087</v>
+        <v>229.1091522321465</v>
       </c>
       <c r="Q44" t="n">
         <v>212.3149906599047</v>
@@ -11356,25 +11356,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K45" t="n">
-        <v>136.7994484083212</v>
+        <v>136.5653954824675</v>
       </c>
       <c r="L45" t="n">
-        <v>137.1532948742138</v>
+        <v>136.8385818314783</v>
       </c>
       <c r="M45" t="n">
-        <v>140.4990339220183</v>
+        <v>140.1317786452013</v>
       </c>
       <c r="N45" t="n">
-        <v>129.6634384984276</v>
+        <v>129.2864630672354</v>
       </c>
       <c r="O45" t="n">
-        <v>141.0609519916142</v>
+        <v>140.7160931202018</v>
       </c>
       <c r="P45" t="n">
-        <v>132.7421998671604</v>
+        <v>132.4654202195568</v>
       </c>
       <c r="Q45" t="n">
-        <v>139.158075972814</v>
+        <v>138.9730561082392</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11438,16 +11438,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L46" t="n">
-        <v>134.0803811992711</v>
+        <v>133.8997196622861</v>
       </c>
       <c r="M46" t="n">
-        <v>138.0777675541624</v>
+        <v>137.8872852940284</v>
       </c>
       <c r="N46" t="n">
-        <v>126.8576920062168</v>
+        <v>126.6717389884799</v>
       </c>
       <c r="O46" t="n">
-        <v>137.6918827141379</v>
+        <v>137.5201250048898</v>
       </c>
       <c r="P46" t="n">
         <v>135.0065633140411</v>
@@ -23230,16 +23230,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>415.2906772136275</v>
+        <v>415.2879682170718</v>
       </c>
       <c r="H11" t="n">
-        <v>339.3512895529531</v>
+        <v>339.3235460419765</v>
       </c>
       <c r="I11" t="n">
-        <v>210.0109347965366</v>
+        <v>209.9064962068211</v>
       </c>
       <c r="J11" t="n">
-        <v>10.92568633953714</v>
+        <v>10.69576364311372</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -23260,19 +23260,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.688322330122688</v>
+        <v>8.395781178313161</v>
       </c>
       <c r="R11" t="n">
-        <v>149.1115350265768</v>
+        <v>148.9413660216818</v>
       </c>
       <c r="S11" t="n">
-        <v>208.7452454656423</v>
+        <v>208.6835142066282</v>
       </c>
       <c r="T11" t="n">
-        <v>223.0430555942821</v>
+        <v>223.0311969618593</v>
       </c>
       <c r="U11" t="n">
-        <v>251.3446880837159</v>
+        <v>251.3444713639914</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,16 +23309,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>137.3370643330219</v>
+        <v>137.3356148920818</v>
       </c>
       <c r="H12" t="n">
-        <v>112.1731234817795</v>
+        <v>112.1591249337519</v>
       </c>
       <c r="I12" t="n">
-        <v>89.17446304009432</v>
+        <v>89.12455904281175</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1369403828616385</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>99.75719264320917</v>
+        <v>99.6672001609758</v>
       </c>
       <c r="S12" t="n">
-        <v>171.5633126132718</v>
+        <v>171.5363898835276</v>
       </c>
       <c r="T12" t="n">
-        <v>200.1387192608593</v>
+        <v>200.1328769967189</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9409575526729</v>
+        <v>225.9408621947163</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,19 +23388,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.9855695223932</v>
+        <v>167.9843543597988</v>
       </c>
       <c r="H13" t="n">
-        <v>162.1790741467838</v>
+        <v>162.1682702466266</v>
       </c>
       <c r="I13" t="n">
-        <v>155.2877864026681</v>
+        <v>155.2512431493756</v>
       </c>
       <c r="J13" t="n">
-        <v>92.97670470683671</v>
+        <v>92.89079271141465</v>
       </c>
       <c r="K13" t="n">
-        <v>21.64096723571891</v>
+        <v>21.49978743611831</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23415,22 +23415,22 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.067145653139296</v>
+        <v>1.920177260816417</v>
       </c>
       <c r="Q13" t="n">
-        <v>85.70904325169438</v>
+        <v>85.60728995481479</v>
       </c>
       <c r="R13" t="n">
-        <v>177.0501454755301</v>
+        <v>176.9955073465141</v>
       </c>
       <c r="S13" t="n">
-        <v>223.9223193484477</v>
+        <v>223.9011423785076</v>
       </c>
       <c r="T13" t="n">
-        <v>227.9224746741831</v>
+        <v>227.9172826158254</v>
       </c>
       <c r="U13" t="n">
-        <v>286.3187342745236</v>
+        <v>286.3186679929276</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,16 +23467,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>415.2906772136275</v>
+        <v>415.2879682170718</v>
       </c>
       <c r="H14" t="n">
-        <v>339.3512895529531</v>
+        <v>339.3235460419765</v>
       </c>
       <c r="I14" t="n">
-        <v>210.0109347965366</v>
+        <v>209.9064962068211</v>
       </c>
       <c r="J14" t="n">
-        <v>10.92568633953714</v>
+        <v>10.69576364311372</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -23497,19 +23497,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.688322330122688</v>
+        <v>8.395781178313161</v>
       </c>
       <c r="R14" t="n">
-        <v>149.1115350265768</v>
+        <v>148.9413660216818</v>
       </c>
       <c r="S14" t="n">
-        <v>208.7452454656423</v>
+        <v>208.6835142066282</v>
       </c>
       <c r="T14" t="n">
-        <v>223.0430555942821</v>
+        <v>223.0311969618593</v>
       </c>
       <c r="U14" t="n">
-        <v>251.3446880837159</v>
+        <v>251.3444713639914</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,16 +23546,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>137.3370643330219</v>
+        <v>137.3356148920818</v>
       </c>
       <c r="H15" t="n">
-        <v>112.1731234817795</v>
+        <v>112.1591249337519</v>
       </c>
       <c r="I15" t="n">
-        <v>89.17446304009432</v>
+        <v>89.12455904281175</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1369403828616385</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>99.75719264320917</v>
+        <v>99.6672001609758</v>
       </c>
       <c r="S15" t="n">
-        <v>171.5633126132718</v>
+        <v>171.5363898835276</v>
       </c>
       <c r="T15" t="n">
-        <v>200.1387192608593</v>
+        <v>200.1328769967189</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9409575526729</v>
+        <v>225.9408621947163</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,19 +23625,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.9855695223932</v>
+        <v>167.9843543597988</v>
       </c>
       <c r="H16" t="n">
-        <v>162.1790741467838</v>
+        <v>162.1682702466266</v>
       </c>
       <c r="I16" t="n">
-        <v>155.2877864026681</v>
+        <v>155.2512431493756</v>
       </c>
       <c r="J16" t="n">
-        <v>92.97670470683671</v>
+        <v>92.89079271141465</v>
       </c>
       <c r="K16" t="n">
-        <v>21.64096723571891</v>
+        <v>21.49978743611831</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23652,22 +23652,22 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.067145653139296</v>
+        <v>1.920177260816417</v>
       </c>
       <c r="Q16" t="n">
-        <v>85.70904325169438</v>
+        <v>85.60728995481479</v>
       </c>
       <c r="R16" t="n">
-        <v>177.0501454755301</v>
+        <v>176.9955073465141</v>
       </c>
       <c r="S16" t="n">
-        <v>223.9223193484477</v>
+        <v>223.9011423785076</v>
       </c>
       <c r="T16" t="n">
-        <v>227.9224746741831</v>
+        <v>227.9172826158254</v>
       </c>
       <c r="U16" t="n">
-        <v>286.3187342745236</v>
+        <v>286.3186679929276</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,16 +23704,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>415.2906772136275</v>
+        <v>415.2879682170718</v>
       </c>
       <c r="H17" t="n">
-        <v>339.3512895529531</v>
+        <v>339.3235460419765</v>
       </c>
       <c r="I17" t="n">
-        <v>210.0109347965366</v>
+        <v>209.9064962068211</v>
       </c>
       <c r="J17" t="n">
-        <v>10.92568633953714</v>
+        <v>10.69576364311372</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23734,19 +23734,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.688322330122688</v>
+        <v>8.395781178313161</v>
       </c>
       <c r="R17" t="n">
-        <v>149.1115350265768</v>
+        <v>148.9413660216818</v>
       </c>
       <c r="S17" t="n">
-        <v>208.7452454656423</v>
+        <v>208.6835142066282</v>
       </c>
       <c r="T17" t="n">
-        <v>223.0430555942821</v>
+        <v>223.0311969618593</v>
       </c>
       <c r="U17" t="n">
-        <v>251.3446880837159</v>
+        <v>251.3444713639914</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,16 +23783,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>137.3370643330219</v>
+        <v>137.3356148920818</v>
       </c>
       <c r="H18" t="n">
-        <v>112.1731234817795</v>
+        <v>112.1591249337519</v>
       </c>
       <c r="I18" t="n">
-        <v>89.17446304009432</v>
+        <v>89.12455904281175</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1369403828616277</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>99.75719264320917</v>
+        <v>99.6672001609758</v>
       </c>
       <c r="S18" t="n">
-        <v>171.5633126132718</v>
+        <v>171.5363898835276</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1387192608593</v>
+        <v>200.1328769967189</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9409575526729</v>
+        <v>225.9408621947163</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,19 +23862,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.9855695223932</v>
+        <v>167.9843543597988</v>
       </c>
       <c r="H19" t="n">
-        <v>162.1790741467838</v>
+        <v>162.1682702466266</v>
       </c>
       <c r="I19" t="n">
-        <v>155.2877864026681</v>
+        <v>155.2512431493756</v>
       </c>
       <c r="J19" t="n">
-        <v>92.97670470683671</v>
+        <v>92.89079271141465</v>
       </c>
       <c r="K19" t="n">
-        <v>21.64096723571891</v>
+        <v>21.49978743611831</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -23889,22 +23889,22 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.067145653139296</v>
+        <v>1.920177260816417</v>
       </c>
       <c r="Q19" t="n">
-        <v>85.70904325169438</v>
+        <v>85.60728995481479</v>
       </c>
       <c r="R19" t="n">
-        <v>177.0501454755301</v>
+        <v>176.9955073465141</v>
       </c>
       <c r="S19" t="n">
-        <v>223.9223193484477</v>
+        <v>223.9011423785076</v>
       </c>
       <c r="T19" t="n">
-        <v>227.9224746741831</v>
+        <v>227.9172826158254</v>
       </c>
       <c r="U19" t="n">
-        <v>286.3187342745236</v>
+        <v>286.3186679929276</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,16 +23941,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>415.2906772136275</v>
+        <v>415.2879682170718</v>
       </c>
       <c r="H20" t="n">
-        <v>339.3512895529531</v>
+        <v>339.3235460419765</v>
       </c>
       <c r="I20" t="n">
-        <v>210.0109347965366</v>
+        <v>209.9064962068211</v>
       </c>
       <c r="J20" t="n">
-        <v>10.92568633953714</v>
+        <v>10.69576364311372</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -23971,19 +23971,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.688322330122688</v>
+        <v>8.395781178313161</v>
       </c>
       <c r="R20" t="n">
-        <v>149.1115350265768</v>
+        <v>148.9413660216818</v>
       </c>
       <c r="S20" t="n">
-        <v>208.7452454656423</v>
+        <v>208.6835142066282</v>
       </c>
       <c r="T20" t="n">
-        <v>223.0430555942821</v>
+        <v>223.0311969618593</v>
       </c>
       <c r="U20" t="n">
-        <v>251.3446880837159</v>
+        <v>251.3444713639914</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,16 +24020,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3370643330219</v>
+        <v>137.3356148920818</v>
       </c>
       <c r="H21" t="n">
-        <v>112.1731234817795</v>
+        <v>112.1591249337519</v>
       </c>
       <c r="I21" t="n">
-        <v>89.17446304009432</v>
+        <v>89.12455904281175</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1369403828616277</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>99.75719264320917</v>
+        <v>99.6672001609758</v>
       </c>
       <c r="S21" t="n">
-        <v>171.5633126132718</v>
+        <v>171.5363898835276</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1387192608593</v>
+        <v>200.1328769967189</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9409575526729</v>
+        <v>225.9408621947163</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,19 +24099,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.9855695223932</v>
+        <v>167.9843543597988</v>
       </c>
       <c r="H22" t="n">
-        <v>162.1790741467838</v>
+        <v>162.1682702466266</v>
       </c>
       <c r="I22" t="n">
-        <v>155.2877864026681</v>
+        <v>155.2512431493756</v>
       </c>
       <c r="J22" t="n">
-        <v>92.97670470683671</v>
+        <v>92.89079271141465</v>
       </c>
       <c r="K22" t="n">
-        <v>21.64096723571891</v>
+        <v>21.49978743611831</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -24126,22 +24126,22 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.067145653139296</v>
+        <v>1.920177260816417</v>
       </c>
       <c r="Q22" t="n">
-        <v>85.70904325169438</v>
+        <v>85.60728995481479</v>
       </c>
       <c r="R22" t="n">
-        <v>177.0501454755301</v>
+        <v>176.9955073465141</v>
       </c>
       <c r="S22" t="n">
-        <v>223.9223193484477</v>
+        <v>223.9011423785076</v>
       </c>
       <c r="T22" t="n">
-        <v>227.9224746741831</v>
+        <v>227.9172826158254</v>
       </c>
       <c r="U22" t="n">
-        <v>286.3187342745236</v>
+        <v>286.3186679929276</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,16 +24178,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>415.2906772136275</v>
+        <v>415.2879682170718</v>
       </c>
       <c r="H23" t="n">
-        <v>339.3512895529531</v>
+        <v>339.3235460419765</v>
       </c>
       <c r="I23" t="n">
-        <v>210.0109347965366</v>
+        <v>209.9064962068211</v>
       </c>
       <c r="J23" t="n">
-        <v>10.92568633953714</v>
+        <v>10.69576364311372</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -24208,19 +24208,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.688322330122688</v>
+        <v>8.395781178313161</v>
       </c>
       <c r="R23" t="n">
-        <v>149.1115350265768</v>
+        <v>148.9413660216818</v>
       </c>
       <c r="S23" t="n">
-        <v>208.7452454656423</v>
+        <v>208.6835142066282</v>
       </c>
       <c r="T23" t="n">
-        <v>223.0430555942821</v>
+        <v>223.0311969618593</v>
       </c>
       <c r="U23" t="n">
-        <v>251.3446880837159</v>
+        <v>251.3444713639914</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,16 +24257,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3370643330219</v>
+        <v>137.3356148920818</v>
       </c>
       <c r="H24" t="n">
-        <v>112.1731234817795</v>
+        <v>112.1591249337519</v>
       </c>
       <c r="I24" t="n">
-        <v>89.17446304009432</v>
+        <v>89.12455904281175</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1369403828616277</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>99.75719264320917</v>
+        <v>99.6672001609758</v>
       </c>
       <c r="S24" t="n">
-        <v>171.5633126132718</v>
+        <v>171.5363898835276</v>
       </c>
       <c r="T24" t="n">
-        <v>200.1387192608593</v>
+        <v>200.1328769967189</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9409575526729</v>
+        <v>225.9408621947163</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,19 +24336,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.9855695223932</v>
+        <v>167.9843543597988</v>
       </c>
       <c r="H25" t="n">
-        <v>162.1790741467838</v>
+        <v>162.1682702466266</v>
       </c>
       <c r="I25" t="n">
-        <v>155.2877864026681</v>
+        <v>155.2512431493756</v>
       </c>
       <c r="J25" t="n">
-        <v>92.97670470683671</v>
+        <v>92.89079271141465</v>
       </c>
       <c r="K25" t="n">
-        <v>21.64096723571891</v>
+        <v>21.49978743611831</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -24363,22 +24363,22 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.067145653139296</v>
+        <v>1.920177260816417</v>
       </c>
       <c r="Q25" t="n">
-        <v>85.70904325169438</v>
+        <v>85.60728995481479</v>
       </c>
       <c r="R25" t="n">
-        <v>177.0501454755301</v>
+        <v>176.9955073465141</v>
       </c>
       <c r="S25" t="n">
-        <v>223.9223193484477</v>
+        <v>223.9011423785076</v>
       </c>
       <c r="T25" t="n">
-        <v>227.9224746741831</v>
+        <v>227.9172826158254</v>
       </c>
       <c r="U25" t="n">
-        <v>286.3187342745236</v>
+        <v>286.3186679929276</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,16 +24415,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>415.2906772136275</v>
+        <v>415.2879682170718</v>
       </c>
       <c r="H26" t="n">
-        <v>339.3512895529531</v>
+        <v>339.3235460419765</v>
       </c>
       <c r="I26" t="n">
-        <v>210.0109347965366</v>
+        <v>209.9064962068211</v>
       </c>
       <c r="J26" t="n">
-        <v>10.92568633953714</v>
+        <v>10.69576364311372</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -24445,19 +24445,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>8.688322330122688</v>
+        <v>8.395781178313161</v>
       </c>
       <c r="R26" t="n">
-        <v>149.1115350265768</v>
+        <v>148.9413660216818</v>
       </c>
       <c r="S26" t="n">
-        <v>208.7452454656423</v>
+        <v>208.6835142066282</v>
       </c>
       <c r="T26" t="n">
-        <v>223.0430555942821</v>
+        <v>223.0311969618593</v>
       </c>
       <c r="U26" t="n">
-        <v>251.3446880837159</v>
+        <v>251.3444713639914</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,16 +24494,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3370643330219</v>
+        <v>137.3356148920818</v>
       </c>
       <c r="H27" t="n">
-        <v>112.1731234817795</v>
+        <v>112.1591249337519</v>
       </c>
       <c r="I27" t="n">
-        <v>89.17446304009432</v>
+        <v>89.12455904281175</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1369403828616277</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>99.75719264320917</v>
+        <v>99.6672001609758</v>
       </c>
       <c r="S27" t="n">
-        <v>171.5633126132718</v>
+        <v>171.5363898835276</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1387192608593</v>
+        <v>200.1328769967189</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9409575526729</v>
+        <v>225.9408621947163</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,19 +24573,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.9855695223932</v>
+        <v>167.9843543597988</v>
       </c>
       <c r="H28" t="n">
-        <v>162.1790741467838</v>
+        <v>162.1682702466266</v>
       </c>
       <c r="I28" t="n">
-        <v>155.2877864026681</v>
+        <v>155.2512431493756</v>
       </c>
       <c r="J28" t="n">
-        <v>92.97670470683671</v>
+        <v>92.89079271141465</v>
       </c>
       <c r="K28" t="n">
-        <v>21.64096723571891</v>
+        <v>21.49978743611831</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -24600,22 +24600,22 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.067145653139296</v>
+        <v>1.920177260816417</v>
       </c>
       <c r="Q28" t="n">
-        <v>85.70904325169438</v>
+        <v>85.60728995481479</v>
       </c>
       <c r="R28" t="n">
-        <v>177.0501454755301</v>
+        <v>176.9955073465141</v>
       </c>
       <c r="S28" t="n">
-        <v>223.9223193484477</v>
+        <v>223.9011423785076</v>
       </c>
       <c r="T28" t="n">
-        <v>227.9224746741831</v>
+        <v>227.9172826158254</v>
       </c>
       <c r="U28" t="n">
-        <v>286.3187342745236</v>
+        <v>286.3186679929276</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,16 +24652,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>415.2906772136275</v>
+        <v>415.2879682170718</v>
       </c>
       <c r="H29" t="n">
-        <v>339.3512895529531</v>
+        <v>339.3235460419765</v>
       </c>
       <c r="I29" t="n">
-        <v>210.0109347965366</v>
+        <v>209.9064962068211</v>
       </c>
       <c r="J29" t="n">
-        <v>10.92568633953714</v>
+        <v>10.69576364311372</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -24682,19 +24682,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8.688322330122688</v>
+        <v>8.395781178313161</v>
       </c>
       <c r="R29" t="n">
-        <v>149.1115350265768</v>
+        <v>148.9413660216818</v>
       </c>
       <c r="S29" t="n">
-        <v>208.7452454656423</v>
+        <v>208.6835142066282</v>
       </c>
       <c r="T29" t="n">
-        <v>223.0430555942821</v>
+        <v>223.0311969618593</v>
       </c>
       <c r="U29" t="n">
-        <v>251.3446880837159</v>
+        <v>251.3444713639914</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,16 +24731,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3370643330219</v>
+        <v>137.3356148920818</v>
       </c>
       <c r="H30" t="n">
-        <v>112.1731234817795</v>
+        <v>112.1591249337519</v>
       </c>
       <c r="I30" t="n">
-        <v>89.17446304009432</v>
+        <v>89.12455904281175</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1369403828616277</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>99.75719264320917</v>
+        <v>99.6672001609758</v>
       </c>
       <c r="S30" t="n">
-        <v>171.5633126132718</v>
+        <v>171.5363898835276</v>
       </c>
       <c r="T30" t="n">
-        <v>200.1387192608593</v>
+        <v>200.1328769967189</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9409575526729</v>
+        <v>225.9408621947163</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,19 +24810,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.9855695223932</v>
+        <v>167.9843543597988</v>
       </c>
       <c r="H31" t="n">
-        <v>162.1790741467838</v>
+        <v>162.1682702466266</v>
       </c>
       <c r="I31" t="n">
-        <v>155.2877864026681</v>
+        <v>155.2512431493756</v>
       </c>
       <c r="J31" t="n">
-        <v>92.97670470683671</v>
+        <v>92.89079271141465</v>
       </c>
       <c r="K31" t="n">
-        <v>21.64096723571891</v>
+        <v>21.49978743611831</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -24837,22 +24837,22 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.067145653139296</v>
+        <v>1.920177260816417</v>
       </c>
       <c r="Q31" t="n">
-        <v>85.70904325169438</v>
+        <v>85.60728995481479</v>
       </c>
       <c r="R31" t="n">
-        <v>177.0501454755301</v>
+        <v>176.9955073465141</v>
       </c>
       <c r="S31" t="n">
-        <v>223.9223193484477</v>
+        <v>223.9011423785076</v>
       </c>
       <c r="T31" t="n">
-        <v>227.9224746741831</v>
+        <v>227.9172826158254</v>
       </c>
       <c r="U31" t="n">
-        <v>286.3187342745236</v>
+        <v>286.3186679929276</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,16 +24889,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>415.2906772136275</v>
+        <v>415.2879682170718</v>
       </c>
       <c r="H32" t="n">
-        <v>339.3512895529531</v>
+        <v>339.3235460419765</v>
       </c>
       <c r="I32" t="n">
-        <v>210.0109347965366</v>
+        <v>209.9064962068211</v>
       </c>
       <c r="J32" t="n">
-        <v>10.92568633953714</v>
+        <v>10.69576364311372</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -24919,19 +24919,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>8.688322330122688</v>
+        <v>8.395781178313161</v>
       </c>
       <c r="R32" t="n">
-        <v>149.1115350265768</v>
+        <v>148.9413660216818</v>
       </c>
       <c r="S32" t="n">
-        <v>208.7452454656423</v>
+        <v>208.6835142066282</v>
       </c>
       <c r="T32" t="n">
-        <v>223.0430555942821</v>
+        <v>223.0311969618593</v>
       </c>
       <c r="U32" t="n">
-        <v>251.3446880837159</v>
+        <v>251.3444713639914</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,16 +24968,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3370643330219</v>
+        <v>137.3356148920818</v>
       </c>
       <c r="H33" t="n">
-        <v>112.1731234817795</v>
+        <v>112.1591249337519</v>
       </c>
       <c r="I33" t="n">
-        <v>89.17446304009432</v>
+        <v>89.12455904281175</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1369403828616385</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>99.75719264320917</v>
+        <v>99.6672001609758</v>
       </c>
       <c r="S33" t="n">
-        <v>171.5633126132718</v>
+        <v>171.5363898835276</v>
       </c>
       <c r="T33" t="n">
-        <v>200.1387192608593</v>
+        <v>200.1328769967189</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9409575526729</v>
+        <v>225.9408621947163</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,19 +25047,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.9855695223932</v>
+        <v>167.9843543597988</v>
       </c>
       <c r="H34" t="n">
-        <v>162.1790741467838</v>
+        <v>162.1682702466266</v>
       </c>
       <c r="I34" t="n">
-        <v>155.2877864026681</v>
+        <v>155.2512431493756</v>
       </c>
       <c r="J34" t="n">
-        <v>92.97670470683671</v>
+        <v>92.89079271141465</v>
       </c>
       <c r="K34" t="n">
-        <v>21.64096723571891</v>
+        <v>21.49978743611831</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -25074,22 +25074,22 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.067145653139296</v>
+        <v>1.920177260816417</v>
       </c>
       <c r="Q34" t="n">
-        <v>85.70904325169438</v>
+        <v>85.60728995481479</v>
       </c>
       <c r="R34" t="n">
-        <v>177.0501454755301</v>
+        <v>176.9955073465141</v>
       </c>
       <c r="S34" t="n">
-        <v>223.9223193484477</v>
+        <v>223.9011423785076</v>
       </c>
       <c r="T34" t="n">
-        <v>227.9224746741831</v>
+        <v>227.9172826158254</v>
       </c>
       <c r="U34" t="n">
-        <v>286.3187342745236</v>
+        <v>286.3186679929276</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,16 +25126,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>415.2906772136275</v>
+        <v>415.2879682170718</v>
       </c>
       <c r="H35" t="n">
-        <v>339.3512895529531</v>
+        <v>339.3235460419765</v>
       </c>
       <c r="I35" t="n">
-        <v>210.0109347965366</v>
+        <v>209.9064962068211</v>
       </c>
       <c r="J35" t="n">
-        <v>10.92568633953714</v>
+        <v>10.69576364311372</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -25156,19 +25156,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>8.688322330122688</v>
+        <v>8.395781178313161</v>
       </c>
       <c r="R35" t="n">
-        <v>149.1115350265768</v>
+        <v>148.9413660216818</v>
       </c>
       <c r="S35" t="n">
-        <v>208.7452454656423</v>
+        <v>208.6835142066282</v>
       </c>
       <c r="T35" t="n">
-        <v>223.0430555942821</v>
+        <v>223.0311969618593</v>
       </c>
       <c r="U35" t="n">
-        <v>251.3446880837159</v>
+        <v>251.3444713639914</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,16 +25205,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>137.3370643330219</v>
+        <v>137.3356148920818</v>
       </c>
       <c r="H36" t="n">
-        <v>112.1731234817795</v>
+        <v>112.1591249337519</v>
       </c>
       <c r="I36" t="n">
-        <v>89.17446304009432</v>
+        <v>89.12455904281175</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1369403828616277</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>99.75719264320917</v>
+        <v>99.6672001609758</v>
       </c>
       <c r="S36" t="n">
-        <v>171.5633126132718</v>
+        <v>171.5363898835276</v>
       </c>
       <c r="T36" t="n">
-        <v>200.1387192608593</v>
+        <v>200.1328769967189</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9409575526729</v>
+        <v>225.9408621947163</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,19 +25284,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.9855695223932</v>
+        <v>167.9843543597988</v>
       </c>
       <c r="H37" t="n">
-        <v>162.1790741467838</v>
+        <v>162.1682702466266</v>
       </c>
       <c r="I37" t="n">
-        <v>155.2877864026681</v>
+        <v>155.2512431493756</v>
       </c>
       <c r="J37" t="n">
-        <v>92.97670470683671</v>
+        <v>92.89079271141465</v>
       </c>
       <c r="K37" t="n">
-        <v>21.64096723571891</v>
+        <v>21.49978743611831</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -25311,22 +25311,22 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.067145653139296</v>
+        <v>1.920177260816417</v>
       </c>
       <c r="Q37" t="n">
-        <v>85.70904325169438</v>
+        <v>85.60728995481479</v>
       </c>
       <c r="R37" t="n">
-        <v>177.0501454755301</v>
+        <v>176.9955073465141</v>
       </c>
       <c r="S37" t="n">
-        <v>223.9223193484477</v>
+        <v>223.9011423785076</v>
       </c>
       <c r="T37" t="n">
-        <v>227.9224746741831</v>
+        <v>227.9172826158254</v>
       </c>
       <c r="U37" t="n">
-        <v>286.3187342745236</v>
+        <v>286.3186679929276</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,16 +25363,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>415.2906772136275</v>
+        <v>415.2879682170718</v>
       </c>
       <c r="H38" t="n">
-        <v>339.3512895529531</v>
+        <v>339.3235460419765</v>
       </c>
       <c r="I38" t="n">
-        <v>210.0109347965366</v>
+        <v>209.9064962068211</v>
       </c>
       <c r="J38" t="n">
-        <v>10.92568633953714</v>
+        <v>10.69576364311372</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25393,19 +25393,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>8.688322330122688</v>
+        <v>8.395781178313161</v>
       </c>
       <c r="R38" t="n">
-        <v>149.1115350265768</v>
+        <v>148.9413660216818</v>
       </c>
       <c r="S38" t="n">
-        <v>208.7452454656423</v>
+        <v>208.6835142066282</v>
       </c>
       <c r="T38" t="n">
-        <v>223.0430555942821</v>
+        <v>223.0311969618593</v>
       </c>
       <c r="U38" t="n">
-        <v>251.3446880837159</v>
+        <v>251.3444713639914</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,16 +25442,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3370643330219</v>
+        <v>137.3356148920818</v>
       </c>
       <c r="H39" t="n">
-        <v>112.1731234817795</v>
+        <v>112.1591249337519</v>
       </c>
       <c r="I39" t="n">
-        <v>89.17446304009432</v>
+        <v>89.12455904281175</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1369403828616385</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>99.75719264320917</v>
+        <v>99.6672001609758</v>
       </c>
       <c r="S39" t="n">
-        <v>171.5633126132718</v>
+        <v>171.5363898835276</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1387192608593</v>
+        <v>200.1328769967189</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9409575526729</v>
+        <v>225.9408621947163</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,19 +25521,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.9855695223932</v>
+        <v>167.9843543597988</v>
       </c>
       <c r="H40" t="n">
-        <v>162.1790741467838</v>
+        <v>162.1682702466266</v>
       </c>
       <c r="I40" t="n">
-        <v>155.2877864026681</v>
+        <v>155.2512431493756</v>
       </c>
       <c r="J40" t="n">
-        <v>92.97670470683671</v>
+        <v>92.89079271141465</v>
       </c>
       <c r="K40" t="n">
-        <v>21.64096723571891</v>
+        <v>21.49978743611831</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -25548,22 +25548,22 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.067145653139296</v>
+        <v>1.920177260816417</v>
       </c>
       <c r="Q40" t="n">
-        <v>85.70904325169438</v>
+        <v>85.60728995481479</v>
       </c>
       <c r="R40" t="n">
-        <v>177.0501454755301</v>
+        <v>176.9955073465141</v>
       </c>
       <c r="S40" t="n">
-        <v>223.9223193484477</v>
+        <v>223.9011423785076</v>
       </c>
       <c r="T40" t="n">
-        <v>227.9224746741831</v>
+        <v>227.9172826158254</v>
       </c>
       <c r="U40" t="n">
-        <v>286.3187342745236</v>
+        <v>286.3186679929276</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,16 +25600,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>415.2906772136275</v>
+        <v>415.2879682170718</v>
       </c>
       <c r="H41" t="n">
-        <v>339.3512895529531</v>
+        <v>339.3235460419765</v>
       </c>
       <c r="I41" t="n">
-        <v>210.0109347965366</v>
+        <v>209.9064962068211</v>
       </c>
       <c r="J41" t="n">
-        <v>10.92568633953714</v>
+        <v>10.69576364311372</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -25630,19 +25630,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>8.688322330122688</v>
+        <v>8.395781178313161</v>
       </c>
       <c r="R41" t="n">
-        <v>149.1115350265768</v>
+        <v>148.9413660216818</v>
       </c>
       <c r="S41" t="n">
-        <v>208.7452454656423</v>
+        <v>208.6835142066282</v>
       </c>
       <c r="T41" t="n">
-        <v>223.0430555942821</v>
+        <v>223.0311969618593</v>
       </c>
       <c r="U41" t="n">
-        <v>251.3446880837159</v>
+        <v>251.3444713639914</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,16 +25679,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>137.3370643330219</v>
+        <v>137.3356148920818</v>
       </c>
       <c r="H42" t="n">
-        <v>112.1731234817795</v>
+        <v>112.1591249337519</v>
       </c>
       <c r="I42" t="n">
-        <v>89.17446304009432</v>
+        <v>89.12455904281175</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1369403828616277</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>99.75719264320917</v>
+        <v>99.6672001609758</v>
       </c>
       <c r="S42" t="n">
-        <v>171.5633126132718</v>
+        <v>171.5363898835276</v>
       </c>
       <c r="T42" t="n">
-        <v>200.1387192608593</v>
+        <v>200.1328769967189</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9409575526729</v>
+        <v>225.9408621947163</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,19 +25758,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.9855695223932</v>
+        <v>167.9843543597988</v>
       </c>
       <c r="H43" t="n">
-        <v>162.1790741467838</v>
+        <v>162.1682702466266</v>
       </c>
       <c r="I43" t="n">
-        <v>155.2877864026681</v>
+        <v>155.2512431493756</v>
       </c>
       <c r="J43" t="n">
-        <v>92.97670470683671</v>
+        <v>92.89079271141465</v>
       </c>
       <c r="K43" t="n">
-        <v>21.64096723571891</v>
+        <v>21.49978743611831</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -25785,22 +25785,22 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.067145653139296</v>
+        <v>1.920177260816417</v>
       </c>
       <c r="Q43" t="n">
-        <v>85.70904325169438</v>
+        <v>85.60728995481479</v>
       </c>
       <c r="R43" t="n">
-        <v>177.0501454755301</v>
+        <v>176.9955073465141</v>
       </c>
       <c r="S43" t="n">
-        <v>223.9223193484477</v>
+        <v>223.9011423785076</v>
       </c>
       <c r="T43" t="n">
-        <v>227.9224746741831</v>
+        <v>227.9172826158254</v>
       </c>
       <c r="U43" t="n">
-        <v>286.3187342745236</v>
+        <v>286.3186679929276</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,16 +25837,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>415.2906772136275</v>
+        <v>415.2879682170718</v>
       </c>
       <c r="H44" t="n">
-        <v>339.3512895529531</v>
+        <v>339.3235460419765</v>
       </c>
       <c r="I44" t="n">
-        <v>210.0109347965366</v>
+        <v>209.9064962068211</v>
       </c>
       <c r="J44" t="n">
-        <v>10.92568633953714</v>
+        <v>10.69576364311372</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -25867,19 +25867,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>8.688322330122688</v>
+        <v>8.395781178313161</v>
       </c>
       <c r="R44" t="n">
-        <v>149.1115350265768</v>
+        <v>148.9413660216818</v>
       </c>
       <c r="S44" t="n">
-        <v>208.7452454656423</v>
+        <v>208.6835142066282</v>
       </c>
       <c r="T44" t="n">
-        <v>223.0430555942821</v>
+        <v>223.0311969618593</v>
       </c>
       <c r="U44" t="n">
-        <v>251.3446880837159</v>
+        <v>251.3444713639914</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,16 +25916,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>137.3370643330219</v>
+        <v>137.3356148920818</v>
       </c>
       <c r="H45" t="n">
-        <v>112.1731234817795</v>
+        <v>112.1591249337519</v>
       </c>
       <c r="I45" t="n">
-        <v>89.17446304009432</v>
+        <v>89.12455904281175</v>
       </c>
       <c r="J45" t="n">
-        <v>0.1369403828616385</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>99.75719264320917</v>
+        <v>99.6672001609758</v>
       </c>
       <c r="S45" t="n">
-        <v>171.5633126132718</v>
+        <v>171.5363898835276</v>
       </c>
       <c r="T45" t="n">
-        <v>200.1387192608593</v>
+        <v>200.1328769967189</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9409575526729</v>
+        <v>225.9408621947163</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,19 +25995,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.9855695223932</v>
+        <v>167.9843543597988</v>
       </c>
       <c r="H46" t="n">
-        <v>162.1790741467838</v>
+        <v>162.1682702466266</v>
       </c>
       <c r="I46" t="n">
-        <v>155.2877864026681</v>
+        <v>155.2512431493756</v>
       </c>
       <c r="J46" t="n">
-        <v>92.97670470683671</v>
+        <v>92.89079271141465</v>
       </c>
       <c r="K46" t="n">
-        <v>21.64096723571891</v>
+        <v>21.49978743611831</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -26022,22 +26022,22 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.067145653139296</v>
+        <v>1.920177260816417</v>
       </c>
       <c r="Q46" t="n">
-        <v>85.70904325169438</v>
+        <v>85.60728995481479</v>
       </c>
       <c r="R46" t="n">
-        <v>177.0501454755301</v>
+        <v>176.9955073465141</v>
       </c>
       <c r="S46" t="n">
-        <v>223.9223193484477</v>
+        <v>223.9011423785076</v>
       </c>
       <c r="T46" t="n">
-        <v>227.9224746741831</v>
+        <v>227.9172826158254</v>
       </c>
       <c r="U46" t="n">
-        <v>286.3187342745236</v>
+        <v>286.3186679929276</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>344415.6888350548</v>
+        <v>344503.7382617116</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>344415.6888350548</v>
+        <v>344503.7382617116</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>344415.6888350548</v>
+        <v>344503.7382617116</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>344415.6888350548</v>
+        <v>344503.7382617116</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>344415.6888350548</v>
+        <v>344503.7382617116</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>344415.6888350548</v>
+        <v>344503.7382617116</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>344415.6888350548</v>
+        <v>344503.7382617116</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>344415.6888350548</v>
+        <v>344503.7382617116</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>344415.6888350548</v>
+        <v>344503.7382617116</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>344415.6888350548</v>
+        <v>344503.7382617116</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>344415.6888350548</v>
+        <v>344503.7382617116</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>344415.6888350548</v>
+        <v>344503.7382617116</v>
       </c>
     </row>
   </sheetData>
@@ -26270,40 +26270,40 @@
         <v>69879.81359544017</v>
       </c>
       <c r="E2" t="n">
-        <v>70024.5927200303</v>
+        <v>70057.1131466228</v>
       </c>
       <c r="F2" t="n">
-        <v>70024.5927200303</v>
+        <v>70057.11314662281</v>
       </c>
       <c r="G2" t="n">
-        <v>70024.5927200303</v>
+        <v>70057.11314662281</v>
       </c>
       <c r="H2" t="n">
-        <v>70024.59272003031</v>
+        <v>70057.11314662281</v>
       </c>
       <c r="I2" t="n">
-        <v>70024.59272003031</v>
+        <v>70057.1131466228</v>
       </c>
       <c r="J2" t="n">
-        <v>70024.59272003031</v>
+        <v>70057.1131466228</v>
       </c>
       <c r="K2" t="n">
-        <v>70024.5927200303</v>
+        <v>70057.1131466228</v>
       </c>
       <c r="L2" t="n">
-        <v>70024.59272003033</v>
+        <v>70057.1131466228</v>
       </c>
       <c r="M2" t="n">
-        <v>70024.5927200303</v>
+        <v>70057.1131466228</v>
       </c>
       <c r="N2" t="n">
-        <v>70024.59272003031</v>
+        <v>70057.11314662283</v>
       </c>
       <c r="O2" t="n">
-        <v>70024.5927200303</v>
+        <v>70057.11314662281</v>
       </c>
       <c r="P2" t="n">
-        <v>70024.5927200303</v>
+        <v>70057.11314662281</v>
       </c>
     </row>
     <row r="3">
@@ -26322,7 +26322,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2410.20900000001</v>
+        <v>2951.592470019559</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37627.59193600624</v>
+        <v>37805.55456035603</v>
       </c>
       <c r="C4" t="n">
-        <v>37627.59193600624</v>
+        <v>37805.55456035603</v>
       </c>
       <c r="D4" t="n">
-        <v>37627.59193600624</v>
+        <v>37805.55456035603</v>
       </c>
       <c r="E4" t="n">
-        <v>37384.78229338329</v>
+        <v>37506.79844271899</v>
       </c>
       <c r="F4" t="n">
-        <v>37384.78229338329</v>
+        <v>37506.79844271899</v>
       </c>
       <c r="G4" t="n">
-        <v>37384.78229338329</v>
+        <v>37506.79844271899</v>
       </c>
       <c r="H4" t="n">
-        <v>37384.78229338329</v>
+        <v>37506.79844271899</v>
       </c>
       <c r="I4" t="n">
-        <v>37384.78229338329</v>
+        <v>37506.79844271899</v>
       </c>
       <c r="J4" t="n">
-        <v>37384.78229338329</v>
+        <v>37506.79844271899</v>
       </c>
       <c r="K4" t="n">
-        <v>37384.78229338329</v>
+        <v>37506.79844271899</v>
       </c>
       <c r="L4" t="n">
-        <v>37384.78229338329</v>
+        <v>37506.79844271899</v>
       </c>
       <c r="M4" t="n">
-        <v>37384.78229338329</v>
+        <v>37506.79844271899</v>
       </c>
       <c r="N4" t="n">
-        <v>37384.78229338329</v>
+        <v>37506.79844271899</v>
       </c>
       <c r="O4" t="n">
-        <v>37384.78229338329</v>
+        <v>37506.79844271899</v>
       </c>
       <c r="P4" t="n">
-        <v>37384.78229338329</v>
+        <v>37506.79844271899</v>
       </c>
     </row>
     <row r="5">
@@ -26426,40 +26426,40 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>65.40000000000028</v>
+        <v>80.09021107268255</v>
       </c>
       <c r="F5" t="n">
-        <v>65.40000000000028</v>
+        <v>80.09021107268255</v>
       </c>
       <c r="G5" t="n">
-        <v>65.40000000000028</v>
+        <v>80.09021107268255</v>
       </c>
       <c r="H5" t="n">
-        <v>65.40000000000028</v>
+        <v>80.09021107268255</v>
       </c>
       <c r="I5" t="n">
-        <v>65.40000000000028</v>
+        <v>80.09021107268255</v>
       </c>
       <c r="J5" t="n">
-        <v>65.40000000000028</v>
+        <v>80.09021107268256</v>
       </c>
       <c r="K5" t="n">
-        <v>65.40000000000028</v>
+        <v>80.09021107268255</v>
       </c>
       <c r="L5" t="n">
-        <v>65.40000000000028</v>
+        <v>80.09021107268255</v>
       </c>
       <c r="M5" t="n">
-        <v>65.40000000000028</v>
+        <v>80.09021107268255</v>
       </c>
       <c r="N5" t="n">
-        <v>65.40000000000028</v>
+        <v>80.09021107268255</v>
       </c>
       <c r="O5" t="n">
-        <v>65.40000000000028</v>
+        <v>80.09021107268255</v>
       </c>
       <c r="P5" t="n">
-        <v>65.40000000000028</v>
+        <v>80.09021107268255</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1375.378340566072</v>
+        <v>-1553.340964915864</v>
       </c>
       <c r="C6" t="n">
-        <v>-1375.378340566072</v>
+        <v>-1553.340964915864</v>
       </c>
       <c r="D6" t="n">
-        <v>-1375.378340566072</v>
+        <v>-1553.340964915864</v>
       </c>
       <c r="E6" t="n">
-        <v>30164.20142664699</v>
+        <v>29518.63202281156</v>
       </c>
       <c r="F6" t="n">
-        <v>32574.410426647</v>
+        <v>32470.22449283113</v>
       </c>
       <c r="G6" t="n">
-        <v>32574.410426647</v>
+        <v>32470.22449283113</v>
       </c>
       <c r="H6" t="n">
-        <v>32574.41042664702</v>
+        <v>32470.22449283113</v>
       </c>
       <c r="I6" t="n">
-        <v>32574.41042664702</v>
+        <v>32470.22449283112</v>
       </c>
       <c r="J6" t="n">
-        <v>32574.41042664702</v>
+        <v>32470.22449283112</v>
       </c>
       <c r="K6" t="n">
-        <v>32574.410426647</v>
+        <v>32470.22449283112</v>
       </c>
       <c r="L6" t="n">
-        <v>32574.41042664703</v>
+        <v>32470.22449283112</v>
       </c>
       <c r="M6" t="n">
-        <v>32574.410426647</v>
+        <v>32470.22449283112</v>
       </c>
       <c r="N6" t="n">
-        <v>32574.41042664702</v>
+        <v>32470.22449283115</v>
       </c>
       <c r="O6" t="n">
-        <v>32574.410426647</v>
+        <v>32470.22449283113</v>
       </c>
       <c r="P6" t="n">
-        <v>32574.410426647</v>
+        <v>32470.22449283113</v>
       </c>
     </row>
   </sheetData>
@@ -26684,40 +26684,40 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3.000000000000012</v>
+        <v>3.673862893242319</v>
       </c>
       <c r="F3" t="n">
-        <v>3.000000000000012</v>
+        <v>3.673862893242319</v>
       </c>
       <c r="G3" t="n">
-        <v>3.000000000000012</v>
+        <v>3.673862893242319</v>
       </c>
       <c r="H3" t="n">
-        <v>3.000000000000012</v>
+        <v>3.673862893242319</v>
       </c>
       <c r="I3" t="n">
-        <v>3.000000000000012</v>
+        <v>3.673862893242319</v>
       </c>
       <c r="J3" t="n">
-        <v>3.000000000000012</v>
+        <v>3.673862893242319</v>
       </c>
       <c r="K3" t="n">
-        <v>3.000000000000012</v>
+        <v>3.673862893242319</v>
       </c>
       <c r="L3" t="n">
-        <v>3.000000000000012</v>
+        <v>3.673862893242319</v>
       </c>
       <c r="M3" t="n">
-        <v>3.000000000000012</v>
+        <v>3.673862893242319</v>
       </c>
       <c r="N3" t="n">
-        <v>3.000000000000012</v>
+        <v>3.673862893242319</v>
       </c>
       <c r="O3" t="n">
-        <v>3.000000000000012</v>
+        <v>3.673862893242319</v>
       </c>
       <c r="P3" t="n">
-        <v>3.000000000000012</v>
+        <v>3.673862893242319</v>
       </c>
     </row>
     <row r="4">
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,7 +26892,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26901,40 +26901,40 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>3.673862893242319</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,16 +26947,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -26968,25 +26968,25 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01206030150753773</v>
+        <v>0.01476929806328569</v>
       </c>
       <c r="H11" t="n">
-        <v>0.123512562814075</v>
+        <v>0.1512560737906246</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4649547738693487</v>
+        <v>0.5693933635848223</v>
       </c>
       <c r="J11" t="n">
-        <v>1.023603015075381</v>
+        <v>1.253525711498795</v>
       </c>
       <c r="K11" t="n">
-        <v>1.534115577889454</v>
+        <v>1.878710098517679</v>
       </c>
       <c r="L11" t="n">
-        <v>1.903206030150762</v>
+        <v>2.330706004121959</v>
       </c>
       <c r="M11" t="n">
-        <v>2.117683417085436</v>
+        <v>2.593359508554916</v>
       </c>
       <c r="N11" t="n">
-        <v>2.151949748743728</v>
+        <v>2.635322776677226</v>
       </c>
       <c r="O11" t="n">
-        <v>2.032025125628149</v>
+        <v>2.488460569060429</v>
       </c>
       <c r="P11" t="n">
-        <v>1.734286432160811</v>
+        <v>2.123843523123063</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.302376884422116</v>
+        <v>1.594918036231644</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7575829145728675</v>
+        <v>0.9277519194678707</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2748241206030163</v>
+        <v>0.3365553796171231</v>
       </c>
       <c r="T11" t="n">
-        <v>0.05279396984924644</v>
+        <v>0.06465260227203315</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0009648241206030181</v>
+        <v>0.001181543845062855</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,49 +31749,49 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.006452830188679272</v>
+        <v>0.007902271128860838</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0623207547169814</v>
+        <v>0.07631930274452442</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2221698113207557</v>
+        <v>0.2720738086033227</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6096509433962291</v>
+        <v>0.7465913262578566</v>
       </c>
       <c r="K12" t="n">
-        <v>1.04199056603774</v>
+        <v>1.276043491891533</v>
       </c>
       <c r="L12" t="n">
-        <v>1.401084905660383</v>
+        <v>1.715797948395859</v>
       </c>
       <c r="M12" t="n">
-        <v>1.635000000000007</v>
+        <v>2.002255276817063</v>
       </c>
       <c r="N12" t="n">
-        <v>1.678273584905667</v>
+        <v>2.05524901609789</v>
       </c>
       <c r="O12" t="n">
-        <v>1.535292452830195</v>
+        <v>1.880151324242604</v>
       </c>
       <c r="P12" t="n">
-        <v>1.232207547169817</v>
+        <v>1.508987194773435</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8236981132075507</v>
+        <v>1.008717977782306</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4006415094339641</v>
+        <v>0.4906339916673423</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1198584905660382</v>
+        <v>0.1467812203102001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02600943396226425</v>
+        <v>0.03185169810273292</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0004245283018867944</v>
+        <v>0.0005198862584776868</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.005409836065573792</v>
+        <v>0.006624998659945164</v>
       </c>
       <c r="H13" t="n">
-        <v>0.04809836065573794</v>
+        <v>0.05890226081296705</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1626885245901646</v>
+        <v>0.1992317778827147</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3824754098360671</v>
+        <v>0.4683874052581231</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6285245901639368</v>
+        <v>0.769704389764538</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8042950819672166</v>
+        <v>0.9849566189522113</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8480163934426262</v>
+        <v>1.038498653576677</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8278524590163974</v>
+        <v>1.013805476753246</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7646557377049215</v>
+        <v>0.9364134469529769</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6542950819672155</v>
+        <v>0.8012634742900948</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4530000000000018</v>
+        <v>0.5547532968795902</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2432459016393452</v>
+        <v>0.2978840306553525</v>
       </c>
       <c r="S13" t="n">
-        <v>0.09427868852459051</v>
+        <v>0.1154556584646807</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02311475409836074</v>
+        <v>0.02830681245612933</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0002950819672131163</v>
+        <v>0.0003613635632697367</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01206030150753773</v>
+        <v>0.01476929806328569</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1235125628140708</v>
+        <v>0.1512560737906246</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4649547738693487</v>
+        <v>0.5693933635848223</v>
       </c>
       <c r="J14" t="n">
-        <v>1.023603015075381</v>
+        <v>1.253525711498795</v>
       </c>
       <c r="K14" t="n">
-        <v>1.534115577889454</v>
+        <v>1.878710098517679</v>
       </c>
       <c r="L14" t="n">
-        <v>1.903206030150762</v>
+        <v>2.330706004121959</v>
       </c>
       <c r="M14" t="n">
-        <v>2.117683417085436</v>
+        <v>2.593359508554916</v>
       </c>
       <c r="N14" t="n">
-        <v>2.151949748743728</v>
+        <v>2.635322776677226</v>
       </c>
       <c r="O14" t="n">
-        <v>2.032025125628149</v>
+        <v>2.488460569060429</v>
       </c>
       <c r="P14" t="n">
-        <v>1.734286432160811</v>
+        <v>2.123843523123063</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.302376884422116</v>
+        <v>1.594918036231644</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7575829145728675</v>
+        <v>0.9277519194678707</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2748241206030163</v>
+        <v>0.3365553796171231</v>
       </c>
       <c r="T14" t="n">
-        <v>0.05279396984924644</v>
+        <v>0.06465260227203315</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0009648241206030181</v>
+        <v>0.001181543845062855</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,49 +31986,49 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.006452830188679272</v>
+        <v>0.007902271128860838</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0623207547169814</v>
+        <v>0.07631930274452442</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2221698113207557</v>
+        <v>0.2720738086033227</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6096509433962291</v>
+        <v>0.7465913262578566</v>
       </c>
       <c r="K15" t="n">
-        <v>1.04199056603774</v>
+        <v>1.276043491891533</v>
       </c>
       <c r="L15" t="n">
-        <v>1.401084905660383</v>
+        <v>1.715797948395859</v>
       </c>
       <c r="M15" t="n">
-        <v>1.635000000000007</v>
+        <v>2.002255276817063</v>
       </c>
       <c r="N15" t="n">
-        <v>1.678273584905667</v>
+        <v>2.05524901609789</v>
       </c>
       <c r="O15" t="n">
-        <v>1.535292452830195</v>
+        <v>1.880151324242604</v>
       </c>
       <c r="P15" t="n">
-        <v>1.232207547169817</v>
+        <v>1.508987194773435</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8236981132075507</v>
+        <v>1.008717977782306</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4006415094339641</v>
+        <v>0.4906339916673423</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1198584905660382</v>
+        <v>0.1467812203102001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.02600943396226425</v>
+        <v>0.03185169810273292</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0004245283018867944</v>
+        <v>0.0005198862584776868</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.005409836065573792</v>
+        <v>0.006624998659945164</v>
       </c>
       <c r="H16" t="n">
-        <v>0.04809836065573794</v>
+        <v>0.05890226081296705</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1626885245901646</v>
+        <v>0.1992317778827147</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3824754098360671</v>
+        <v>0.4683874052581231</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6285245901639368</v>
+        <v>0.769704389764538</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8042950819672166</v>
+        <v>0.9849566189522113</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8480163934426262</v>
+        <v>1.038498653576677</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8278524590163974</v>
+        <v>1.013805476753246</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7646557377049215</v>
+        <v>0.9364134469529769</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6542950819672155</v>
+        <v>0.8012634742900948</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4530000000000018</v>
+        <v>0.5547532968795902</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2432459016393452</v>
+        <v>0.2978840306553525</v>
       </c>
       <c r="S16" t="n">
-        <v>0.09427868852459051</v>
+        <v>0.1154556584646807</v>
       </c>
       <c r="T16" t="n">
-        <v>0.02311475409836074</v>
+        <v>0.02830681245612933</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0002950819672131163</v>
+        <v>0.0003613635632697367</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01206030150753773</v>
+        <v>0.01476929806328569</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1235125628140708</v>
+        <v>0.1512560737906246</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4649547738693487</v>
+        <v>0.5693933635848223</v>
       </c>
       <c r="J17" t="n">
-        <v>1.023603015075381</v>
+        <v>1.253525711498795</v>
       </c>
       <c r="K17" t="n">
-        <v>1.534115577889454</v>
+        <v>1.878710098517679</v>
       </c>
       <c r="L17" t="n">
-        <v>1.903206030150762</v>
+        <v>2.330706004121959</v>
       </c>
       <c r="M17" t="n">
-        <v>2.117683417085436</v>
+        <v>2.593359508554916</v>
       </c>
       <c r="N17" t="n">
-        <v>2.151949748743728</v>
+        <v>2.635322776677226</v>
       </c>
       <c r="O17" t="n">
-        <v>2.032025125628149</v>
+        <v>2.488460569060429</v>
       </c>
       <c r="P17" t="n">
-        <v>1.734286432160811</v>
+        <v>2.123843523123063</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.302376884422116</v>
+        <v>1.594918036231644</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7575829145728675</v>
+        <v>0.9277519194678707</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2748241206030163</v>
+        <v>0.3365553796171231</v>
       </c>
       <c r="T17" t="n">
-        <v>0.05279396984924644</v>
+        <v>0.06465260227203315</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0009648241206030181</v>
+        <v>0.001181543845062855</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,49 +32223,49 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.006452830188679272</v>
+        <v>0.007902271128860838</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0623207547169814</v>
+        <v>0.07631930274452442</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2221698113207557</v>
+        <v>0.2720738086033227</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6096509433962291</v>
+        <v>0.7465913262578566</v>
       </c>
       <c r="K18" t="n">
-        <v>1.04199056603774</v>
+        <v>1.276043491891533</v>
       </c>
       <c r="L18" t="n">
-        <v>1.401084905660383</v>
+        <v>1.715797948395859</v>
       </c>
       <c r="M18" t="n">
-        <v>1.635000000000007</v>
+        <v>2.002255276817063</v>
       </c>
       <c r="N18" t="n">
-        <v>1.678273584905667</v>
+        <v>2.05524901609789</v>
       </c>
       <c r="O18" t="n">
-        <v>1.535292452830195</v>
+        <v>1.880151324242604</v>
       </c>
       <c r="P18" t="n">
-        <v>1.232207547169817</v>
+        <v>1.508987194773435</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.8236981132075507</v>
+        <v>1.008717977782306</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4006415094339641</v>
+        <v>0.4906339916673423</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1198584905660382</v>
+        <v>0.1467812203102001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.02600943396226425</v>
+        <v>0.03185169810273292</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0004245283018867944</v>
+        <v>0.0005198862584776868</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.005409836065573792</v>
+        <v>0.006624998659945164</v>
       </c>
       <c r="H19" t="n">
-        <v>0.04809836065573794</v>
+        <v>0.05890226081296705</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1626885245901646</v>
+        <v>0.1992317778827147</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3824754098360671</v>
+        <v>0.4683874052581231</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6285245901639368</v>
+        <v>0.769704389764538</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8042950819672166</v>
+        <v>0.9849566189522113</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8480163934426262</v>
+        <v>1.038498653576677</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8278524590163974</v>
+        <v>1.013805476753246</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7646557377049215</v>
+        <v>0.9364134469529769</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6542950819672155</v>
+        <v>0.8012634742900948</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.4530000000000018</v>
+        <v>0.5547532968795902</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2432459016393452</v>
+        <v>0.2978840306553525</v>
       </c>
       <c r="S19" t="n">
-        <v>0.09427868852459051</v>
+        <v>0.1154556584646807</v>
       </c>
       <c r="T19" t="n">
-        <v>0.02311475409836074</v>
+        <v>0.02830681245612933</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0002950819672131163</v>
+        <v>0.0003613635632697367</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01206030150753773</v>
+        <v>0.01476929806328569</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1235125628140708</v>
+        <v>0.1512560737906246</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4649547738693487</v>
+        <v>0.5693933635848223</v>
       </c>
       <c r="J20" t="n">
-        <v>1.023603015075381</v>
+        <v>1.253525711498795</v>
       </c>
       <c r="K20" t="n">
-        <v>1.534115577889454</v>
+        <v>1.878710098517679</v>
       </c>
       <c r="L20" t="n">
-        <v>1.903206030150762</v>
+        <v>2.330706004121959</v>
       </c>
       <c r="M20" t="n">
-        <v>2.117683417085436</v>
+        <v>2.593359508554916</v>
       </c>
       <c r="N20" t="n">
-        <v>2.151949748743728</v>
+        <v>2.635322776677226</v>
       </c>
       <c r="O20" t="n">
-        <v>2.032025125628149</v>
+        <v>2.488460569060429</v>
       </c>
       <c r="P20" t="n">
-        <v>1.734286432160811</v>
+        <v>2.123843523123063</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.302376884422116</v>
+        <v>1.594918036231644</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7575829145728675</v>
+        <v>0.9277519194678707</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2748241206030163</v>
+        <v>0.3365553796171231</v>
       </c>
       <c r="T20" t="n">
-        <v>0.05279396984924644</v>
+        <v>0.06465260227203315</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0009648241206030181</v>
+        <v>0.001181543845062855</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,49 +32460,49 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.006452830188679272</v>
+        <v>0.007902271128860838</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0623207547169814</v>
+        <v>0.07631930274452442</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2221698113207557</v>
+        <v>0.2720738086033227</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6096509433962291</v>
+        <v>0.7465913262578566</v>
       </c>
       <c r="K21" t="n">
-        <v>1.04199056603774</v>
+        <v>1.276043491891533</v>
       </c>
       <c r="L21" t="n">
-        <v>1.401084905660383</v>
+        <v>1.715797948395859</v>
       </c>
       <c r="M21" t="n">
-        <v>1.635000000000007</v>
+        <v>2.002255276817063</v>
       </c>
       <c r="N21" t="n">
-        <v>1.678273584905667</v>
+        <v>2.05524901609789</v>
       </c>
       <c r="O21" t="n">
-        <v>1.535292452830195</v>
+        <v>1.880151324242604</v>
       </c>
       <c r="P21" t="n">
-        <v>1.232207547169817</v>
+        <v>1.508987194773435</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8236981132075507</v>
+        <v>1.008717977782306</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4006415094339641</v>
+        <v>0.4906339916673423</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1198584905660382</v>
+        <v>0.1467812203102001</v>
       </c>
       <c r="T21" t="n">
-        <v>0.02600943396226425</v>
+        <v>0.03185169810273292</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0004245283018867944</v>
+        <v>0.0005198862584776868</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.005409836065573792</v>
+        <v>0.006624998659945164</v>
       </c>
       <c r="H22" t="n">
-        <v>0.04809836065573794</v>
+        <v>0.05890226081296705</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1626885245901646</v>
+        <v>0.1992317778827147</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3824754098360671</v>
+        <v>0.4683874052581231</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6285245901639368</v>
+        <v>0.769704389764538</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8042950819672166</v>
+        <v>0.9849566189522113</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8480163934426262</v>
+        <v>1.038498653576677</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8278524590163974</v>
+        <v>1.013805476753246</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7646557377049215</v>
+        <v>0.9364134469529769</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6542950819672155</v>
+        <v>0.8012634742900948</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.4530000000000018</v>
+        <v>0.5547532968795902</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2432459016393452</v>
+        <v>0.2978840306553525</v>
       </c>
       <c r="S22" t="n">
-        <v>0.09427868852459051</v>
+        <v>0.1154556584646807</v>
       </c>
       <c r="T22" t="n">
-        <v>0.02311475409836074</v>
+        <v>0.02830681245612933</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0002950819672131163</v>
+        <v>0.0003613635632697367</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01206030150753773</v>
+        <v>0.01476929806328569</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1235125628140708</v>
+        <v>0.1512560737906246</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4649547738693487</v>
+        <v>0.5693933635848223</v>
       </c>
       <c r="J23" t="n">
-        <v>1.023603015075381</v>
+        <v>1.253525711498795</v>
       </c>
       <c r="K23" t="n">
-        <v>1.534115577889454</v>
+        <v>1.878710098517679</v>
       </c>
       <c r="L23" t="n">
-        <v>1.903206030150762</v>
+        <v>2.330706004121959</v>
       </c>
       <c r="M23" t="n">
-        <v>2.117683417085436</v>
+        <v>2.593359508554916</v>
       </c>
       <c r="N23" t="n">
-        <v>2.151949748743728</v>
+        <v>2.635322776677226</v>
       </c>
       <c r="O23" t="n">
-        <v>2.032025125628149</v>
+        <v>2.488460569060429</v>
       </c>
       <c r="P23" t="n">
-        <v>1.734286432160811</v>
+        <v>2.123843523123063</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.302376884422116</v>
+        <v>1.594918036231644</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7575829145728675</v>
+        <v>0.9277519194678707</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2748241206030163</v>
+        <v>0.3365553796171231</v>
       </c>
       <c r="T23" t="n">
-        <v>0.05279396984924644</v>
+        <v>0.06465260227203315</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0009648241206030181</v>
+        <v>0.001181543845062855</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,49 +32697,49 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.006452830188679272</v>
+        <v>0.007902271128860838</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0623207547169814</v>
+        <v>0.07631930274452442</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2221698113207557</v>
+        <v>0.2720738086033227</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6096509433962291</v>
+        <v>0.7465913262578566</v>
       </c>
       <c r="K24" t="n">
-        <v>1.04199056603774</v>
+        <v>1.276043491891533</v>
       </c>
       <c r="L24" t="n">
-        <v>1.401084905660383</v>
+        <v>1.715797948395859</v>
       </c>
       <c r="M24" t="n">
-        <v>1.635000000000007</v>
+        <v>2.002255276817063</v>
       </c>
       <c r="N24" t="n">
-        <v>1.678273584905667</v>
+        <v>2.05524901609789</v>
       </c>
       <c r="O24" t="n">
-        <v>1.535292452830195</v>
+        <v>1.880151324242604</v>
       </c>
       <c r="P24" t="n">
-        <v>1.232207547169817</v>
+        <v>1.508987194773435</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.8236981132075507</v>
+        <v>1.008717977782306</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4006415094339641</v>
+        <v>0.4906339916673423</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1198584905660382</v>
+        <v>0.1467812203102001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.02600943396226425</v>
+        <v>0.03185169810273292</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0004245283018867944</v>
+        <v>0.0005198862584776868</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.005409836065573792</v>
+        <v>0.006624998659945164</v>
       </c>
       <c r="H25" t="n">
-        <v>0.04809836065573794</v>
+        <v>0.05890226081296705</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1626885245901646</v>
+        <v>0.1992317778827147</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3824754098360671</v>
+        <v>0.4683874052581231</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6285245901639368</v>
+        <v>0.769704389764538</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8042950819672166</v>
+        <v>0.9849566189522113</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8480163934426262</v>
+        <v>1.038498653576677</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8278524590163974</v>
+        <v>1.013805476753246</v>
       </c>
       <c r="O25" t="n">
-        <v>0.7646557377049215</v>
+        <v>0.9364134469529769</v>
       </c>
       <c r="P25" t="n">
-        <v>0.6542950819672155</v>
+        <v>0.8012634742900948</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.4530000000000018</v>
+        <v>0.5547532968795902</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2432459016393452</v>
+        <v>0.2978840306553525</v>
       </c>
       <c r="S25" t="n">
-        <v>0.09427868852459051</v>
+        <v>0.1154556584646807</v>
       </c>
       <c r="T25" t="n">
-        <v>0.02311475409836074</v>
+        <v>0.02830681245612933</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0002950819672131163</v>
+        <v>0.0003613635632697367</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01206030150753773</v>
+        <v>0.01476929806328569</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1235125628140708</v>
+        <v>0.1512560737906247</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4649547738693487</v>
+        <v>0.5693933635848223</v>
       </c>
       <c r="J26" t="n">
-        <v>1.023603015075381</v>
+        <v>1.253525711498795</v>
       </c>
       <c r="K26" t="n">
-        <v>1.534115577889454</v>
+        <v>1.878710098517679</v>
       </c>
       <c r="L26" t="n">
-        <v>1.903206030150762</v>
+        <v>2.330706004121959</v>
       </c>
       <c r="M26" t="n">
-        <v>2.117683417085436</v>
+        <v>2.593359508554916</v>
       </c>
       <c r="N26" t="n">
-        <v>2.151949748743728</v>
+        <v>2.635322776677227</v>
       </c>
       <c r="O26" t="n">
-        <v>2.032025125628149</v>
+        <v>2.488460569060429</v>
       </c>
       <c r="P26" t="n">
-        <v>1.734286432160811</v>
+        <v>2.123843523123063</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.302376884422116</v>
+        <v>1.594918036231644</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7575829145728675</v>
+        <v>0.9277519194678707</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2748241206030163</v>
+        <v>0.3365553796171231</v>
       </c>
       <c r="T26" t="n">
-        <v>0.05279396984924644</v>
+        <v>0.06465260227203316</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0009648241206030181</v>
+        <v>0.001181543845062855</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,49 +32934,49 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.006452830188679272</v>
+        <v>0.007902271128860838</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0623207547169814</v>
+        <v>0.07631930274452442</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2221698113207557</v>
+        <v>0.2720738086033228</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6096509433962291</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K27" t="n">
-        <v>1.04199056603774</v>
+        <v>1.276043491891533</v>
       </c>
       <c r="L27" t="n">
-        <v>1.401084905660383</v>
+        <v>1.715797948395859</v>
       </c>
       <c r="M27" t="n">
-        <v>1.635000000000007</v>
+        <v>2.002255276817064</v>
       </c>
       <c r="N27" t="n">
-        <v>1.678273584905667</v>
+        <v>2.05524901609789</v>
       </c>
       <c r="O27" t="n">
-        <v>1.535292452830195</v>
+        <v>1.880151324242605</v>
       </c>
       <c r="P27" t="n">
-        <v>1.232207547169817</v>
+        <v>1.508987194773435</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.8236981132075507</v>
+        <v>1.008717977782306</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4006415094339641</v>
+        <v>0.4906339916673424</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1198584905660382</v>
+        <v>0.1467812203102001</v>
       </c>
       <c r="T27" t="n">
-        <v>0.02600943396226425</v>
+        <v>0.03185169810273293</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0004245283018867944</v>
+        <v>0.000519886258477687</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.005409836065573792</v>
+        <v>0.006624998659945164</v>
       </c>
       <c r="H28" t="n">
-        <v>0.04809836065573794</v>
+        <v>0.05890226081296705</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1626885245901646</v>
+        <v>0.1992317778827147</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3824754098360671</v>
+        <v>0.4683874052581232</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6285245901639368</v>
+        <v>0.7697043897645381</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8042950819672166</v>
+        <v>0.9849566189522113</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8480163934426262</v>
+        <v>1.038498653576677</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8278524590163974</v>
+        <v>1.013805476753246</v>
       </c>
       <c r="O28" t="n">
-        <v>0.7646557377049215</v>
+        <v>0.936413446952977</v>
       </c>
       <c r="P28" t="n">
-        <v>0.6542950819672155</v>
+        <v>0.8012634742900949</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.4530000000000018</v>
+        <v>0.5547532968795902</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2432459016393452</v>
+        <v>0.2978840306553525</v>
       </c>
       <c r="S28" t="n">
-        <v>0.09427868852459051</v>
+        <v>0.1154556584646807</v>
       </c>
       <c r="T28" t="n">
-        <v>0.02311475409836074</v>
+        <v>0.02830681245612933</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0002950819672131163</v>
+        <v>0.0003613635632697367</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01206030150753773</v>
+        <v>0.01476929806328569</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1235125628140708</v>
+        <v>0.1512560737906246</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4649547738693487</v>
+        <v>0.5693933635848223</v>
       </c>
       <c r="J29" t="n">
-        <v>1.023603015075381</v>
+        <v>1.253525711498795</v>
       </c>
       <c r="K29" t="n">
-        <v>1.534115577889454</v>
+        <v>1.878710098517679</v>
       </c>
       <c r="L29" t="n">
-        <v>1.903206030150762</v>
+        <v>2.330706004121959</v>
       </c>
       <c r="M29" t="n">
-        <v>2.117683417085436</v>
+        <v>2.593359508554916</v>
       </c>
       <c r="N29" t="n">
-        <v>2.151949748743728</v>
+        <v>2.635322776677226</v>
       </c>
       <c r="O29" t="n">
-        <v>2.032025125628149</v>
+        <v>2.488460569060429</v>
       </c>
       <c r="P29" t="n">
-        <v>1.734286432160811</v>
+        <v>2.123843523123063</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.302376884422116</v>
+        <v>1.594918036231644</v>
       </c>
       <c r="R29" t="n">
-        <v>0.7575829145728675</v>
+        <v>0.9277519194678707</v>
       </c>
       <c r="S29" t="n">
-        <v>0.2748241206030163</v>
+        <v>0.3365553796171231</v>
       </c>
       <c r="T29" t="n">
-        <v>0.05279396984924644</v>
+        <v>0.06465260227203315</v>
       </c>
       <c r="U29" t="n">
-        <v>0.0009648241206030181</v>
+        <v>0.001181543845062855</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,49 +33171,49 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.006452830188679272</v>
+        <v>0.007902271128860838</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0623207547169814</v>
+        <v>0.07631930274452442</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2221698113207557</v>
+        <v>0.2720738086033227</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6096509433962291</v>
+        <v>0.7465913262578566</v>
       </c>
       <c r="K30" t="n">
-        <v>1.04199056603774</v>
+        <v>1.276043491891533</v>
       </c>
       <c r="L30" t="n">
-        <v>1.401084905660383</v>
+        <v>1.715797948395859</v>
       </c>
       <c r="M30" t="n">
-        <v>1.635000000000007</v>
+        <v>2.002255276817063</v>
       </c>
       <c r="N30" t="n">
-        <v>1.678273584905667</v>
+        <v>2.05524901609789</v>
       </c>
       <c r="O30" t="n">
-        <v>1.535292452830195</v>
+        <v>1.880151324242604</v>
       </c>
       <c r="P30" t="n">
-        <v>1.232207547169817</v>
+        <v>1.508987194773435</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.8236981132075507</v>
+        <v>1.008717977782306</v>
       </c>
       <c r="R30" t="n">
-        <v>0.4006415094339641</v>
+        <v>0.4906339916673423</v>
       </c>
       <c r="S30" t="n">
-        <v>0.1198584905660382</v>
+        <v>0.1467812203102001</v>
       </c>
       <c r="T30" t="n">
-        <v>0.02600943396226425</v>
+        <v>0.03185169810273292</v>
       </c>
       <c r="U30" t="n">
-        <v>0.0004245283018867944</v>
+        <v>0.0005198862584776868</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.005409836065573792</v>
+        <v>0.006624998659945164</v>
       </c>
       <c r="H31" t="n">
-        <v>0.04809836065573794</v>
+        <v>0.05890226081296705</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1626885245901646</v>
+        <v>0.1992317778827147</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3824754098360671</v>
+        <v>0.4683874052581231</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6285245901639368</v>
+        <v>0.769704389764538</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8042950819672166</v>
+        <v>0.9849566189522113</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8480163934426262</v>
+        <v>1.038498653576677</v>
       </c>
       <c r="N31" t="n">
-        <v>0.8278524590163974</v>
+        <v>1.013805476753246</v>
       </c>
       <c r="O31" t="n">
-        <v>0.7646557377049215</v>
+        <v>0.9364134469529769</v>
       </c>
       <c r="P31" t="n">
-        <v>0.6542950819672155</v>
+        <v>0.8012634742900948</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.4530000000000018</v>
+        <v>0.5547532968795902</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2432459016393452</v>
+        <v>0.2978840306553525</v>
       </c>
       <c r="S31" t="n">
-        <v>0.09427868852459051</v>
+        <v>0.1154556584646807</v>
       </c>
       <c r="T31" t="n">
-        <v>0.02311475409836074</v>
+        <v>0.02830681245612933</v>
       </c>
       <c r="U31" t="n">
-        <v>0.0002950819672131163</v>
+        <v>0.0003613635632697367</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.01206030150753773</v>
+        <v>0.01476929806328569</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1235125628140708</v>
+        <v>0.1512560737906246</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4649547738693487</v>
+        <v>0.5693933635848223</v>
       </c>
       <c r="J32" t="n">
-        <v>1.023603015075381</v>
+        <v>1.253525711498795</v>
       </c>
       <c r="K32" t="n">
-        <v>1.534115577889454</v>
+        <v>1.878710098517679</v>
       </c>
       <c r="L32" t="n">
-        <v>1.903206030150762</v>
+        <v>2.330706004121959</v>
       </c>
       <c r="M32" t="n">
-        <v>2.117683417085436</v>
+        <v>2.593359508554916</v>
       </c>
       <c r="N32" t="n">
-        <v>2.151949748743728</v>
+        <v>2.635322776677226</v>
       </c>
       <c r="O32" t="n">
-        <v>2.032025125628149</v>
+        <v>2.488460569060429</v>
       </c>
       <c r="P32" t="n">
-        <v>1.734286432160811</v>
+        <v>2.123843523123063</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.302376884422116</v>
+        <v>1.594918036231644</v>
       </c>
       <c r="R32" t="n">
-        <v>0.7575829145728675</v>
+        <v>0.9277519194678707</v>
       </c>
       <c r="S32" t="n">
-        <v>0.2748241206030163</v>
+        <v>0.3365553796171231</v>
       </c>
       <c r="T32" t="n">
-        <v>0.05279396984924644</v>
+        <v>0.06465260227203315</v>
       </c>
       <c r="U32" t="n">
-        <v>0.0009648241206030181</v>
+        <v>0.001181543845062855</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,49 +33408,49 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.006452830188679272</v>
+        <v>0.007902271128860838</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0623207547169814</v>
+        <v>0.07631930274452442</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2221698113207557</v>
+        <v>0.2720738086033227</v>
       </c>
       <c r="J33" t="n">
-        <v>0.6096509433962291</v>
+        <v>0.7465913262578566</v>
       </c>
       <c r="K33" t="n">
-        <v>1.04199056603774</v>
+        <v>1.276043491891533</v>
       </c>
       <c r="L33" t="n">
-        <v>1.401084905660383</v>
+        <v>1.715797948395859</v>
       </c>
       <c r="M33" t="n">
-        <v>1.635000000000007</v>
+        <v>2.002255276817063</v>
       </c>
       <c r="N33" t="n">
-        <v>1.678273584905667</v>
+        <v>2.05524901609789</v>
       </c>
       <c r="O33" t="n">
-        <v>1.535292452830195</v>
+        <v>1.880151324242604</v>
       </c>
       <c r="P33" t="n">
-        <v>1.232207547169817</v>
+        <v>1.508987194773435</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.8236981132075507</v>
+        <v>1.008717977782306</v>
       </c>
       <c r="R33" t="n">
-        <v>0.4006415094339641</v>
+        <v>0.4906339916673423</v>
       </c>
       <c r="S33" t="n">
-        <v>0.1198584905660382</v>
+        <v>0.1467812203102001</v>
       </c>
       <c r="T33" t="n">
-        <v>0.02600943396226425</v>
+        <v>0.03185169810273292</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0004245283018867944</v>
+        <v>0.0005198862584776868</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.005409836065573792</v>
+        <v>0.006624998659945164</v>
       </c>
       <c r="H34" t="n">
-        <v>0.04809836065573794</v>
+        <v>0.05890226081296705</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1626885245901646</v>
+        <v>0.1992317778827147</v>
       </c>
       <c r="J34" t="n">
-        <v>0.3824754098360671</v>
+        <v>0.4683874052581231</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6285245901639368</v>
+        <v>0.769704389764538</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8042950819672166</v>
+        <v>0.9849566189522113</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8480163934426262</v>
+        <v>1.038498653576677</v>
       </c>
       <c r="N34" t="n">
-        <v>0.8278524590163974</v>
+        <v>1.013805476753246</v>
       </c>
       <c r="O34" t="n">
-        <v>0.7646557377049215</v>
+        <v>0.9364134469529769</v>
       </c>
       <c r="P34" t="n">
-        <v>0.6542950819672155</v>
+        <v>0.8012634742900948</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.4530000000000018</v>
+        <v>0.5547532968795902</v>
       </c>
       <c r="R34" t="n">
-        <v>0.2432459016393452</v>
+        <v>0.2978840306553525</v>
       </c>
       <c r="S34" t="n">
-        <v>0.09427868852459051</v>
+        <v>0.1154556584646807</v>
       </c>
       <c r="T34" t="n">
-        <v>0.02311475409836074</v>
+        <v>0.02830681245612933</v>
       </c>
       <c r="U34" t="n">
-        <v>0.0002950819672131163</v>
+        <v>0.0003613635632697367</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.01206030150753773</v>
+        <v>0.01476929806328569</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1235125628140708</v>
+        <v>0.1512560737906246</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4649547738693487</v>
+        <v>0.5693933635848223</v>
       </c>
       <c r="J35" t="n">
-        <v>1.023603015075381</v>
+        <v>1.253525711498795</v>
       </c>
       <c r="K35" t="n">
-        <v>1.534115577889454</v>
+        <v>1.878710098517679</v>
       </c>
       <c r="L35" t="n">
-        <v>1.903206030150762</v>
+        <v>2.330706004121959</v>
       </c>
       <c r="M35" t="n">
-        <v>2.117683417085436</v>
+        <v>2.593359508554916</v>
       </c>
       <c r="N35" t="n">
-        <v>2.151949748743728</v>
+        <v>2.635322776677226</v>
       </c>
       <c r="O35" t="n">
-        <v>2.032025125628149</v>
+        <v>2.488460569060429</v>
       </c>
       <c r="P35" t="n">
-        <v>1.734286432160811</v>
+        <v>2.123843523123063</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.302376884422116</v>
+        <v>1.594918036231644</v>
       </c>
       <c r="R35" t="n">
-        <v>0.7575829145728675</v>
+        <v>0.9277519194678707</v>
       </c>
       <c r="S35" t="n">
-        <v>0.2748241206030163</v>
+        <v>0.3365553796171231</v>
       </c>
       <c r="T35" t="n">
-        <v>0.05279396984924644</v>
+        <v>0.06465260227203315</v>
       </c>
       <c r="U35" t="n">
-        <v>0.0009648241206030181</v>
+        <v>0.001181543845062855</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,49 +33645,49 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.006452830188679272</v>
+        <v>0.007902271128860838</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0623207547169814</v>
+        <v>0.07631930274452442</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2221698113207557</v>
+        <v>0.2720738086033227</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6096509433962291</v>
+        <v>0.7465913262578566</v>
       </c>
       <c r="K36" t="n">
-        <v>1.04199056603774</v>
+        <v>1.276043491891533</v>
       </c>
       <c r="L36" t="n">
-        <v>1.401084905660383</v>
+        <v>1.715797948395859</v>
       </c>
       <c r="M36" t="n">
-        <v>1.635000000000007</v>
+        <v>2.002255276817063</v>
       </c>
       <c r="N36" t="n">
-        <v>1.678273584905667</v>
+        <v>2.05524901609789</v>
       </c>
       <c r="O36" t="n">
-        <v>1.535292452830195</v>
+        <v>1.880151324242604</v>
       </c>
       <c r="P36" t="n">
-        <v>1.232207547169817</v>
+        <v>1.508987194773435</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.8236981132075507</v>
+        <v>1.008717977782306</v>
       </c>
       <c r="R36" t="n">
-        <v>0.4006415094339641</v>
+        <v>0.4906339916673423</v>
       </c>
       <c r="S36" t="n">
-        <v>0.1198584905660382</v>
+        <v>0.1467812203102001</v>
       </c>
       <c r="T36" t="n">
-        <v>0.02600943396226425</v>
+        <v>0.03185169810273292</v>
       </c>
       <c r="U36" t="n">
-        <v>0.0004245283018867944</v>
+        <v>0.0005198862584776868</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.005409836065573792</v>
+        <v>0.006624998659945164</v>
       </c>
       <c r="H37" t="n">
-        <v>0.04809836065573794</v>
+        <v>0.05890226081296705</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1626885245901646</v>
+        <v>0.1992317778827147</v>
       </c>
       <c r="J37" t="n">
-        <v>0.3824754098360671</v>
+        <v>0.4683874052581231</v>
       </c>
       <c r="K37" t="n">
-        <v>0.6285245901639368</v>
+        <v>0.769704389764538</v>
       </c>
       <c r="L37" t="n">
-        <v>0.8042950819672166</v>
+        <v>0.9849566189522113</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8480163934426262</v>
+        <v>1.038498653576677</v>
       </c>
       <c r="N37" t="n">
-        <v>0.8278524590163974</v>
+        <v>1.013805476753246</v>
       </c>
       <c r="O37" t="n">
-        <v>0.7646557377049215</v>
+        <v>0.9364134469529769</v>
       </c>
       <c r="P37" t="n">
-        <v>0.6542950819672155</v>
+        <v>0.8012634742900948</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.4530000000000018</v>
+        <v>0.5547532968795902</v>
       </c>
       <c r="R37" t="n">
-        <v>0.2432459016393452</v>
+        <v>0.2978840306553525</v>
       </c>
       <c r="S37" t="n">
-        <v>0.09427868852459051</v>
+        <v>0.1154556584646807</v>
       </c>
       <c r="T37" t="n">
-        <v>0.02311475409836074</v>
+        <v>0.02830681245612933</v>
       </c>
       <c r="U37" t="n">
-        <v>0.0002950819672131163</v>
+        <v>0.0003613635632697367</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.01206030150753773</v>
+        <v>0.01476929806328569</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1235125628140708</v>
+        <v>0.1512560737906246</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4649547738693487</v>
+        <v>0.5693933635848223</v>
       </c>
       <c r="J38" t="n">
-        <v>1.023603015075381</v>
+        <v>1.253525711498795</v>
       </c>
       <c r="K38" t="n">
-        <v>1.534115577889454</v>
+        <v>1.878710098517679</v>
       </c>
       <c r="L38" t="n">
-        <v>1.903206030150762</v>
+        <v>2.330706004121959</v>
       </c>
       <c r="M38" t="n">
-        <v>2.117683417085436</v>
+        <v>2.593359508554916</v>
       </c>
       <c r="N38" t="n">
-        <v>2.151949748743728</v>
+        <v>2.635322776677226</v>
       </c>
       <c r="O38" t="n">
-        <v>2.032025125628149</v>
+        <v>2.488460569060429</v>
       </c>
       <c r="P38" t="n">
-        <v>1.734286432160811</v>
+        <v>2.123843523123063</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.302376884422116</v>
+        <v>1.594918036231644</v>
       </c>
       <c r="R38" t="n">
-        <v>0.7575829145728675</v>
+        <v>0.9277519194678707</v>
       </c>
       <c r="S38" t="n">
-        <v>0.2748241206030163</v>
+        <v>0.3365553796171231</v>
       </c>
       <c r="T38" t="n">
-        <v>0.05279396984924644</v>
+        <v>0.06465260227203315</v>
       </c>
       <c r="U38" t="n">
-        <v>0.0009648241206030181</v>
+        <v>0.001181543845062855</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,49 +33882,49 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.006452830188679272</v>
+        <v>0.007902271128860838</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0623207547169814</v>
+        <v>0.07631930274452442</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2221698113207557</v>
+        <v>0.2720738086033227</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6096509433962291</v>
+        <v>0.7465913262578566</v>
       </c>
       <c r="K39" t="n">
-        <v>1.04199056603774</v>
+        <v>1.276043491891533</v>
       </c>
       <c r="L39" t="n">
-        <v>1.401084905660383</v>
+        <v>1.715797948395859</v>
       </c>
       <c r="M39" t="n">
-        <v>1.635000000000007</v>
+        <v>2.002255276817063</v>
       </c>
       <c r="N39" t="n">
-        <v>1.678273584905667</v>
+        <v>2.05524901609789</v>
       </c>
       <c r="O39" t="n">
-        <v>1.535292452830195</v>
+        <v>1.880151324242604</v>
       </c>
       <c r="P39" t="n">
-        <v>1.232207547169817</v>
+        <v>1.508987194773435</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.8236981132075507</v>
+        <v>1.008717977782306</v>
       </c>
       <c r="R39" t="n">
-        <v>0.4006415094339641</v>
+        <v>0.4906339916673423</v>
       </c>
       <c r="S39" t="n">
-        <v>0.1198584905660382</v>
+        <v>0.1467812203102001</v>
       </c>
       <c r="T39" t="n">
-        <v>0.02600943396226425</v>
+        <v>0.03185169810273292</v>
       </c>
       <c r="U39" t="n">
-        <v>0.0004245283018867944</v>
+        <v>0.0005198862584776868</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.005409836065573792</v>
+        <v>0.006624998659945164</v>
       </c>
       <c r="H40" t="n">
-        <v>0.04809836065573794</v>
+        <v>0.05890226081296705</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1626885245901646</v>
+        <v>0.1992317778827147</v>
       </c>
       <c r="J40" t="n">
-        <v>0.3824754098360671</v>
+        <v>0.4683874052581231</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6285245901639368</v>
+        <v>0.769704389764538</v>
       </c>
       <c r="L40" t="n">
-        <v>0.8042950819672166</v>
+        <v>0.9849566189522113</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8480163934426262</v>
+        <v>1.038498653576677</v>
       </c>
       <c r="N40" t="n">
-        <v>0.8278524590163974</v>
+        <v>1.013805476753246</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7646557377049215</v>
+        <v>0.9364134469529769</v>
       </c>
       <c r="P40" t="n">
-        <v>0.6542950819672155</v>
+        <v>0.8012634742900948</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.4530000000000018</v>
+        <v>0.5547532968795902</v>
       </c>
       <c r="R40" t="n">
-        <v>0.2432459016393452</v>
+        <v>0.2978840306553525</v>
       </c>
       <c r="S40" t="n">
-        <v>0.09427868852459051</v>
+        <v>0.1154556584646807</v>
       </c>
       <c r="T40" t="n">
-        <v>0.02311475409836074</v>
+        <v>0.02830681245612933</v>
       </c>
       <c r="U40" t="n">
-        <v>0.0002950819672131163</v>
+        <v>0.0003613635632697367</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.01206030150753773</v>
+        <v>0.01476929806328569</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1235125628140708</v>
+        <v>0.1512560737906246</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4649547738693487</v>
+        <v>0.5693933635848223</v>
       </c>
       <c r="J41" t="n">
-        <v>1.023603015075381</v>
+        <v>1.253525711498795</v>
       </c>
       <c r="K41" t="n">
-        <v>1.534115577889454</v>
+        <v>1.878710098517679</v>
       </c>
       <c r="L41" t="n">
-        <v>1.903206030150762</v>
+        <v>2.330706004121959</v>
       </c>
       <c r="M41" t="n">
-        <v>2.117683417085436</v>
+        <v>2.593359508554916</v>
       </c>
       <c r="N41" t="n">
-        <v>2.151949748743728</v>
+        <v>2.635322776677226</v>
       </c>
       <c r="O41" t="n">
-        <v>2.032025125628149</v>
+        <v>2.488460569060429</v>
       </c>
       <c r="P41" t="n">
-        <v>1.734286432160811</v>
+        <v>2.123843523123063</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.302376884422116</v>
+        <v>1.594918036231644</v>
       </c>
       <c r="R41" t="n">
-        <v>0.7575829145728675</v>
+        <v>0.9277519194678707</v>
       </c>
       <c r="S41" t="n">
-        <v>0.2748241206030163</v>
+        <v>0.3365553796171231</v>
       </c>
       <c r="T41" t="n">
-        <v>0.05279396984924644</v>
+        <v>0.06465260227203315</v>
       </c>
       <c r="U41" t="n">
-        <v>0.0009648241206030181</v>
+        <v>0.001181543845062855</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,49 +34119,49 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.006452830188679272</v>
+        <v>0.007902271128860838</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0623207547169814</v>
+        <v>0.07631930274452442</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2221698113207557</v>
+        <v>0.2720738086033227</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6096509433962291</v>
+        <v>0.7465913262578566</v>
       </c>
       <c r="K42" t="n">
-        <v>1.04199056603774</v>
+        <v>1.276043491891533</v>
       </c>
       <c r="L42" t="n">
-        <v>1.401084905660383</v>
+        <v>1.715797948395859</v>
       </c>
       <c r="M42" t="n">
-        <v>1.635000000000007</v>
+        <v>2.002255276817063</v>
       </c>
       <c r="N42" t="n">
-        <v>1.678273584905667</v>
+        <v>2.05524901609789</v>
       </c>
       <c r="O42" t="n">
-        <v>1.535292452830195</v>
+        <v>1.880151324242604</v>
       </c>
       <c r="P42" t="n">
-        <v>1.232207547169817</v>
+        <v>1.508987194773435</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.8236981132075507</v>
+        <v>1.008717977782306</v>
       </c>
       <c r="R42" t="n">
-        <v>0.4006415094339641</v>
+        <v>0.4906339916673423</v>
       </c>
       <c r="S42" t="n">
-        <v>0.1198584905660382</v>
+        <v>0.1467812203102001</v>
       </c>
       <c r="T42" t="n">
-        <v>0.02600943396226425</v>
+        <v>0.03185169810273292</v>
       </c>
       <c r="U42" t="n">
-        <v>0.0004245283018867944</v>
+        <v>0.0005198862584776868</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.005409836065573792</v>
+        <v>0.006624998659945164</v>
       </c>
       <c r="H43" t="n">
-        <v>0.04809836065573794</v>
+        <v>0.05890226081296705</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1626885245901646</v>
+        <v>0.1992317778827147</v>
       </c>
       <c r="J43" t="n">
-        <v>0.3824754098360671</v>
+        <v>0.4683874052581231</v>
       </c>
       <c r="K43" t="n">
-        <v>0.6285245901639368</v>
+        <v>0.769704389764538</v>
       </c>
       <c r="L43" t="n">
-        <v>0.8042950819672166</v>
+        <v>0.9849566189522113</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8480163934426262</v>
+        <v>1.038498653576677</v>
       </c>
       <c r="N43" t="n">
-        <v>0.8278524590163974</v>
+        <v>1.013805476753246</v>
       </c>
       <c r="O43" t="n">
-        <v>0.7646557377049215</v>
+        <v>0.9364134469529769</v>
       </c>
       <c r="P43" t="n">
-        <v>0.6542950819672155</v>
+        <v>0.8012634742900948</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.4530000000000018</v>
+        <v>0.5547532968795902</v>
       </c>
       <c r="R43" t="n">
-        <v>0.2432459016393452</v>
+        <v>0.2978840306553525</v>
       </c>
       <c r="S43" t="n">
-        <v>0.09427868852459051</v>
+        <v>0.1154556584646807</v>
       </c>
       <c r="T43" t="n">
-        <v>0.02311475409836074</v>
+        <v>0.02830681245612933</v>
       </c>
       <c r="U43" t="n">
-        <v>0.0002950819672131163</v>
+        <v>0.0003613635632697367</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01206030150753773</v>
+        <v>0.01476929806328569</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1235125628140708</v>
+        <v>0.1512560737906246</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4649547738693487</v>
+        <v>0.5693933635848223</v>
       </c>
       <c r="J44" t="n">
-        <v>1.023603015075381</v>
+        <v>1.253525711498795</v>
       </c>
       <c r="K44" t="n">
-        <v>1.534115577889454</v>
+        <v>1.878710098517679</v>
       </c>
       <c r="L44" t="n">
-        <v>1.903206030150762</v>
+        <v>2.330706004121959</v>
       </c>
       <c r="M44" t="n">
-        <v>2.117683417085436</v>
+        <v>2.593359508554916</v>
       </c>
       <c r="N44" t="n">
-        <v>2.151949748743728</v>
+        <v>2.635322776677226</v>
       </c>
       <c r="O44" t="n">
-        <v>2.032025125628149</v>
+        <v>2.488460569060429</v>
       </c>
       <c r="P44" t="n">
-        <v>1.734286432160811</v>
+        <v>2.123843523123063</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.302376884422116</v>
+        <v>1.594918036231644</v>
       </c>
       <c r="R44" t="n">
-        <v>0.7575829145728675</v>
+        <v>0.9277519194678707</v>
       </c>
       <c r="S44" t="n">
-        <v>0.2748241206030163</v>
+        <v>0.3365553796171231</v>
       </c>
       <c r="T44" t="n">
-        <v>0.05279396984924644</v>
+        <v>0.06465260227203315</v>
       </c>
       <c r="U44" t="n">
-        <v>0.0009648241206030181</v>
+        <v>0.001181543845062855</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,49 +34356,49 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.006452830188679272</v>
+        <v>0.007902271128860838</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0623207547169814</v>
+        <v>0.07631930274452442</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2221698113207557</v>
+        <v>0.2720738086033227</v>
       </c>
       <c r="J45" t="n">
-        <v>0.6096509433962291</v>
+        <v>0.7465913262578566</v>
       </c>
       <c r="K45" t="n">
-        <v>1.04199056603774</v>
+        <v>1.276043491891533</v>
       </c>
       <c r="L45" t="n">
-        <v>1.401084905660383</v>
+        <v>1.715797948395859</v>
       </c>
       <c r="M45" t="n">
-        <v>1.635000000000007</v>
+        <v>2.002255276817063</v>
       </c>
       <c r="N45" t="n">
-        <v>1.678273584905667</v>
+        <v>2.05524901609789</v>
       </c>
       <c r="O45" t="n">
-        <v>1.535292452830195</v>
+        <v>1.880151324242604</v>
       </c>
       <c r="P45" t="n">
-        <v>1.232207547169817</v>
+        <v>1.508987194773435</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.8236981132075507</v>
+        <v>1.008717977782306</v>
       </c>
       <c r="R45" t="n">
-        <v>0.4006415094339641</v>
+        <v>0.4906339916673423</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1198584905660382</v>
+        <v>0.1467812203102001</v>
       </c>
       <c r="T45" t="n">
-        <v>0.02600943396226425</v>
+        <v>0.03185169810273292</v>
       </c>
       <c r="U45" t="n">
-        <v>0.0004245283018867944</v>
+        <v>0.0005198862584776868</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.005409836065573792</v>
+        <v>0.006624998659945164</v>
       </c>
       <c r="H46" t="n">
-        <v>0.04809836065573794</v>
+        <v>0.05890226081296705</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1626885245901646</v>
+        <v>0.1992317778827147</v>
       </c>
       <c r="J46" t="n">
-        <v>0.3824754098360671</v>
+        <v>0.4683874052581231</v>
       </c>
       <c r="K46" t="n">
-        <v>0.6285245901639368</v>
+        <v>0.769704389764538</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8042950819672166</v>
+        <v>0.9849566189522113</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8480163934426262</v>
+        <v>1.038498653576677</v>
       </c>
       <c r="N46" t="n">
-        <v>0.8278524590163974</v>
+        <v>1.013805476753246</v>
       </c>
       <c r="O46" t="n">
-        <v>0.7646557377049215</v>
+        <v>0.9364134469529769</v>
       </c>
       <c r="P46" t="n">
-        <v>0.6542950819672155</v>
+        <v>0.8012634742900948</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.4530000000000018</v>
+        <v>0.5547532968795902</v>
       </c>
       <c r="R46" t="n">
-        <v>0.2432459016393452</v>
+        <v>0.2978840306553525</v>
       </c>
       <c r="S46" t="n">
-        <v>0.09427868852459051</v>
+        <v>0.1154556584646807</v>
       </c>
       <c r="T46" t="n">
-        <v>0.02311475409836074</v>
+        <v>0.02830681245612933</v>
       </c>
       <c r="U46" t="n">
-        <v>0.0002950819672131163</v>
+        <v>0.0003613635632697367</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
